--- a/empirical/realized_shocks_Norway.xlsx
+++ b/empirical/realized_shocks_Norway.xlsx
@@ -88,9 +88,7 @@
       <c r="B2" s="1">
         <v>0.30533015727996826</v>
       </c>
-      <c r="C2" s="1">
-        <v>-0.25277885794639587</v>
-      </c>
+      <c r="C2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1">
@@ -100,7 +98,7 @@
         <v>-0.047001522034406662</v>
       </c>
       <c r="C3" s="1">
-        <v>0.42586112022399902</v>
+        <v>0.42485737800598145</v>
       </c>
     </row>
     <row r="4">
@@ -111,7 +109,7 @@
         <v>-0.23476018011569977</v>
       </c>
       <c r="C4" s="1">
-        <v>0.24844799935817719</v>
+        <v>0.082105621695518494</v>
       </c>
     </row>
     <row r="5">
@@ -122,7 +120,7 @@
         <v>0.32987970113754272</v>
       </c>
       <c r="C5" s="1">
-        <v>0.3638184666633606</v>
+        <v>0.33263713121414185</v>
       </c>
     </row>
     <row r="6">
@@ -133,7 +131,7 @@
         <v>-0.21339298784732819</v>
       </c>
       <c r="C6" s="1">
-        <v>0.14328601956367493</v>
+        <v>0.14049288630485535</v>
       </c>
     </row>
     <row r="7">
@@ -144,7 +142,7 @@
         <v>-0.10610231757164001</v>
       </c>
       <c r="C7" s="1">
-        <v>0.18667426705360413</v>
+        <v>0.035711634904146195</v>
       </c>
     </row>
     <row r="8">
@@ -155,7 +153,7 @@
         <v>0.27987131476402283</v>
       </c>
       <c r="C8" s="1">
-        <v>0.33795201778411865</v>
+        <v>0.1387898325920105</v>
       </c>
     </row>
     <row r="9">
@@ -166,7 +164,7 @@
         <v>-0.12883338332176208</v>
       </c>
       <c r="C9" s="1">
-        <v>0.04215862974524498</v>
+        <v>0.26153373718261719</v>
       </c>
     </row>
     <row r="10">
@@ -177,7 +175,7 @@
         <v>-0.70256572961807251</v>
       </c>
       <c r="C10" s="1">
-        <v>0.34553977847099304</v>
+        <v>0.1769181489944458</v>
       </c>
     </row>
     <row r="11">
@@ -188,7 +186,7 @@
         <v>-0.070641838014125824</v>
       </c>
       <c r="C11" s="1">
-        <v>0.053368344902992249</v>
+        <v>0.041550695896148682</v>
       </c>
     </row>
     <row r="12">
@@ -199,7 +197,7 @@
         <v>-0.28704166412353516</v>
       </c>
       <c r="C12" s="1">
-        <v>0.22955186665058136</v>
+        <v>0.17287443578243256</v>
       </c>
     </row>
     <row r="13">
@@ -210,7 +208,7 @@
         <v>-0.0010847488883882761</v>
       </c>
       <c r="C13" s="1">
-        <v>-0.53515821695327759</v>
+        <v>-0.18305774033069611</v>
       </c>
     </row>
     <row r="14">
@@ -221,7 +219,7 @@
         <v>0.82541710138320923</v>
       </c>
       <c r="C14" s="1">
-        <v>0.20457199215888977</v>
+        <v>0.081420369446277619</v>
       </c>
     </row>
     <row r="15">
@@ -232,7 +230,7 @@
         <v>-0.3647819459438324</v>
       </c>
       <c r="C15" s="1">
-        <v>0.47240179777145386</v>
+        <v>0.42679810523986816</v>
       </c>
     </row>
     <row r="16">
@@ -243,7 +241,7 @@
         <v>-0.25021731853485107</v>
       </c>
       <c r="C16" s="1">
-        <v>0.23241372406482697</v>
+        <v>0.043385852128267288</v>
       </c>
     </row>
     <row r="17">
@@ -254,7 +252,7 @@
         <v>-0.15701991319656372</v>
       </c>
       <c r="C17" s="1">
-        <v>0.079250238835811615</v>
+        <v>0.0085810422897338867</v>
       </c>
     </row>
     <row r="18">
@@ -265,7 +263,7 @@
         <v>-0.11837708950042725</v>
       </c>
       <c r="C18" s="1">
-        <v>0.20930957794189453</v>
+        <v>0.161656454205513</v>
       </c>
     </row>
     <row r="19">
@@ -276,7 +274,7 @@
         <v>0.31169483065605164</v>
       </c>
       <c r="C19" s="1">
-        <v>0.16289205849170685</v>
+        <v>-0.013961946591734886</v>
       </c>
     </row>
     <row r="20">
@@ -287,7 +285,7 @@
         <v>0.062562264502048492</v>
       </c>
       <c r="C20" s="1">
-        <v>0.24974739551544189</v>
+        <v>0.21553061902523041</v>
       </c>
     </row>
     <row r="21">
@@ -298,7 +296,7 @@
         <v>-0.17247705161571503</v>
       </c>
       <c r="C21" s="1">
-        <v>-0.10137710720300674</v>
+        <v>0.25159996747970581</v>
       </c>
     </row>
     <row r="22">
@@ -309,7 +307,7 @@
         <v>-0.073824189603328705</v>
       </c>
       <c r="C22" s="1">
-        <v>0.053804241120815277</v>
+        <v>0.045081984251737595</v>
       </c>
     </row>
     <row r="23">
@@ -320,7 +318,7 @@
         <v>-0.26840218901634216</v>
       </c>
       <c r="C23" s="1">
-        <v>-0.20390136539936066</v>
+        <v>0.13712134957313538</v>
       </c>
     </row>
     <row r="24">
@@ -328,10 +326,10 @@
         <v>197611</v>
       </c>
       <c r="B24" s="1">
-        <v>0.098477348685264587</v>
+        <v>0.098477348685264588</v>
       </c>
       <c r="C24" s="1">
-        <v>-0.07144077867269516</v>
+        <v>-0.081711374223232269</v>
       </c>
     </row>
     <row r="25">
@@ -342,7 +340,7 @@
         <v>-0.077006533741950989</v>
       </c>
       <c r="C25" s="1">
-        <v>0.23224218189716339</v>
+        <v>0.24226105213165283</v>
       </c>
     </row>
     <row r="26">
@@ -353,7 +351,7 @@
         <v>-0.089281320571899414</v>
       </c>
       <c r="C26" s="1">
-        <v>0.17140369117259979</v>
+        <v>-0.1271282285451889</v>
       </c>
     </row>
     <row r="27">
@@ -364,7 +362,7 @@
         <v>-0.24748960137367249</v>
       </c>
       <c r="C27" s="1">
-        <v>0.11589334160089493</v>
+        <v>0.069356285035610199</v>
       </c>
     </row>
     <row r="28">
@@ -375,7 +373,7 @@
         <v>-0.023361204192042351</v>
       </c>
       <c r="C28" s="1">
-        <v>0.17801201343536377</v>
+        <v>-0.067976512014865875</v>
       </c>
     </row>
     <row r="29">
@@ -386,7 +384,7 @@
         <v>-0.28840550780296326</v>
       </c>
       <c r="C29" s="1">
-        <v>-0.035649426281452179</v>
+        <v>-0.084453836083412171</v>
       </c>
     </row>
     <row r="30">
@@ -397,7 +395,7 @@
         <v>-0.20566442608833313</v>
       </c>
       <c r="C30" s="1">
-        <v>-0.076768830418586731</v>
+        <v>-0.13754411041736603</v>
       </c>
     </row>
     <row r="31">
@@ -408,7 +406,7 @@
         <v>0.089839547872543335</v>
       </c>
       <c r="C31" s="1">
-        <v>0.55528140068054199</v>
+        <v>0.4821244478225708</v>
       </c>
     </row>
     <row r="32">
@@ -419,7 +417,7 @@
         <v>-0.082461997866630554</v>
       </c>
       <c r="C32" s="1">
-        <v>-0.1477673202753067</v>
+        <v>-0.33983641862869263</v>
       </c>
     </row>
     <row r="33">
@@ -430,7 +428,7 @@
         <v>-0.246125727891922</v>
       </c>
       <c r="C33" s="1">
-        <v>0.14046704769134521</v>
+        <v>0.53617411851882935</v>
       </c>
     </row>
     <row r="34">
@@ -441,7 +439,7 @@
         <v>0.15348654985427856</v>
       </c>
       <c r="C34" s="1">
-        <v>0.24518881738185883</v>
+        <v>0.25949808955192566</v>
       </c>
     </row>
     <row r="35">
@@ -452,7 +450,7 @@
         <v>-0.15520143508911133</v>
       </c>
       <c r="C35" s="1">
-        <v>0.32191431522369385</v>
+        <v>0.35702377557754517</v>
       </c>
     </row>
     <row r="36">
@@ -463,7 +461,7 @@
         <v>-0.20975600183010101</v>
       </c>
       <c r="C36" s="1">
-        <v>-0.076970390975475311</v>
+        <v>0.28854507207870483</v>
       </c>
     </row>
     <row r="37">
@@ -474,7 +472,7 @@
         <v>-0.24157951772212982</v>
       </c>
       <c r="C37" s="1">
-        <v>0.1847379207611084</v>
+        <v>0.15936446189880371</v>
       </c>
     </row>
     <row r="38">
@@ -485,7 +483,7 @@
         <v>-0.30340802669525146</v>
       </c>
       <c r="C38" s="1">
-        <v>0.13689376413822174</v>
+        <v>-0.22928899526596069</v>
       </c>
     </row>
     <row r="39">
@@ -496,7 +494,7 @@
         <v>-0.017451122403144836</v>
       </c>
       <c r="C39" s="1">
-        <v>0.18859496712684631</v>
+        <v>0.24869407713413239</v>
       </c>
     </row>
     <row r="40">
@@ -507,7 +505,7 @@
         <v>-0.0092679383233189583</v>
       </c>
       <c r="C40" s="1">
-        <v>0.20580469071865082</v>
+        <v>0.06786741316318512</v>
       </c>
     </row>
     <row r="41">
@@ -518,7 +516,7 @@
         <v>0.043013527989387512</v>
       </c>
       <c r="C41" s="1">
-        <v>0.19656151533126831</v>
+        <v>0.23804482817649841</v>
       </c>
     </row>
     <row r="42">
@@ -529,7 +527,7 @@
         <v>0.11393448710441589</v>
       </c>
       <c r="C42" s="1">
-        <v>-0.10538308322429657</v>
+        <v>-0.074928440153598785</v>
       </c>
     </row>
     <row r="43">
@@ -540,7 +538,7 @@
         <v>-0.3129551112651825</v>
       </c>
       <c r="C43" s="1">
-        <v>0.37499025464057922</v>
+        <v>0.34664827585220337</v>
       </c>
     </row>
     <row r="44">
@@ -551,7 +549,7 @@
         <v>0.1980394572019577</v>
       </c>
       <c r="C44" s="1">
-        <v>0.098810426890850067</v>
+        <v>-0.054439999163150787</v>
       </c>
     </row>
     <row r="45">
@@ -562,7 +560,7 @@
         <v>0.68584829568862915</v>
       </c>
       <c r="C45" s="1">
-        <v>-0.14255441725254059</v>
+        <v>0.20013472437858582</v>
       </c>
     </row>
     <row r="46">
@@ -573,7 +571,7 @@
         <v>0.11984456330537796</v>
       </c>
       <c r="C46" s="1">
-        <v>0.14375323057174683</v>
+        <v>-0.07106645405292511</v>
       </c>
     </row>
     <row r="47">
@@ -584,7 +582,7 @@
         <v>-0.69483715295791626</v>
       </c>
       <c r="C47" s="1">
-        <v>-0.17501267790794373</v>
+        <v>0.11617989093065262</v>
       </c>
     </row>
     <row r="48">
@@ -595,7 +593,7 @@
         <v>0.14030253887176514</v>
       </c>
       <c r="C48" s="1">
-        <v>0.22643101215362549</v>
+        <v>0.29920321702957153</v>
       </c>
     </row>
     <row r="49">
@@ -606,7 +604,7 @@
         <v>-0.08337123692035675</v>
       </c>
       <c r="C49" s="1">
-        <v>-0.22632679343223572</v>
+        <v>0.14160232245922089</v>
       </c>
     </row>
     <row r="50">
@@ -617,7 +615,7 @@
         <v>0.32260572910308838</v>
       </c>
       <c r="C50" s="1">
-        <v>0.027218414470553398</v>
+        <v>0.15938064455986023</v>
       </c>
     </row>
     <row r="51">
@@ -628,7 +626,7 @@
         <v>0.48263251781463623</v>
       </c>
       <c r="C51" s="1">
-        <v>0.0785178542137146</v>
+        <v>0.091439753770828247</v>
       </c>
     </row>
     <row r="52">
@@ -639,7 +637,7 @@
         <v>0.093931138515472412</v>
       </c>
       <c r="C52" s="1">
-        <v>0.16855919361114502</v>
+        <v>0.17689885199069977</v>
       </c>
     </row>
     <row r="53">
@@ -650,7 +648,7 @@
         <v>0.63493072986602783</v>
       </c>
       <c r="C53" s="1">
-        <v>0.1144370511174202</v>
+        <v>0.13554200530052185</v>
       </c>
     </row>
     <row r="54">
@@ -661,7 +659,7 @@
         <v>0.50809133052825928</v>
       </c>
       <c r="C54" s="1">
-        <v>0.17900481820106506</v>
+        <v>0.20281252264976502</v>
       </c>
     </row>
     <row r="55">
@@ -672,7 +670,7 @@
         <v>0.71994495391845703</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.034123342484235764</v>
+        <v>-0.044115513563156128</v>
       </c>
     </row>
     <row r="56">
@@ -683,7 +681,7 @@
         <v>-0.11792246997356415</v>
       </c>
       <c r="C56" s="1">
-        <v>0.20147910714149475</v>
+        <v>0.10832998901605606</v>
       </c>
     </row>
     <row r="57">
@@ -694,7 +692,7 @@
         <v>0.021191708743572235</v>
       </c>
       <c r="C57" s="1">
-        <v>0.033314567059278488</v>
+        <v>0.41073384881019592</v>
       </c>
     </row>
     <row r="58">
@@ -702,10 +700,10 @@
         <v>197909</v>
       </c>
       <c r="B58" s="1">
-        <v>0.55628120899200439</v>
+        <v>0.5562812089920044</v>
       </c>
       <c r="C58" s="1">
-        <v>0.21625770628452301</v>
+        <v>0.22040863335132599</v>
       </c>
     </row>
     <row r="59">
@@ -716,7 +714,7 @@
         <v>0.41443929076194763</v>
       </c>
       <c r="C59" s="1">
-        <v>-0.15249636769294739</v>
+        <v>-0.24190154671669006</v>
       </c>
     </row>
     <row r="60">
@@ -727,7 +725,7 @@
         <v>0.75358688831329346</v>
       </c>
       <c r="C60" s="1">
-        <v>0.23429982364177704</v>
+        <v>0.19041542708873749</v>
       </c>
     </row>
     <row r="61">
@@ -738,7 +736,7 @@
         <v>-0.17020395398139954</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.23495842516422272</v>
+        <v>0.11482327431440353</v>
       </c>
     </row>
     <row r="62">
@@ -749,7 +747,7 @@
         <v>0.01028078980743885</v>
       </c>
       <c r="C62" s="1">
-        <v>0.24002128839492798</v>
+        <v>0.013321380130946636</v>
       </c>
     </row>
     <row r="63">
@@ -760,7 +758,7 @@
         <v>-0.3120458722114563</v>
       </c>
       <c r="C63" s="1">
-        <v>0.25058579444885254</v>
+        <v>-0.039180204272270203</v>
       </c>
     </row>
     <row r="64">
@@ -771,7 +769,7 @@
         <v>-1.0908124446868896</v>
       </c>
       <c r="C64" s="1">
-        <v>0.18855616450309753</v>
+        <v>0.021912673488259315</v>
       </c>
     </row>
     <row r="65">
@@ -782,7 +780,7 @@
         <v>0.43262416124343872</v>
       </c>
       <c r="C65" s="1">
-        <v>0.11980973184108734</v>
+        <v>0.063603684306144714</v>
       </c>
     </row>
     <row r="66">
@@ -793,7 +791,7 @@
         <v>0.48626947402954102</v>
       </c>
       <c r="C66" s="1">
-        <v>-0.0034084755461663008</v>
+        <v>-0.17933599650859833</v>
       </c>
     </row>
     <row r="67">
@@ -804,7 +802,7 @@
         <v>-0.13428884744644165</v>
       </c>
       <c r="C67" s="1">
-        <v>0.21682316064834595</v>
+        <v>0.0090930769219994545</v>
       </c>
     </row>
     <row r="68">
@@ -815,7 +813,7 @@
         <v>-0.14201740920543671</v>
       </c>
       <c r="C68" s="1">
-        <v>-0.56254738569259644</v>
+        <v>-0.74437761306762695</v>
       </c>
     </row>
     <row r="69">
@@ -826,7 +824,7 @@
         <v>-0.29340636730194092</v>
       </c>
       <c r="C69" s="1">
-        <v>0.81658816337585449</v>
+        <v>0.8206828236579895</v>
       </c>
     </row>
     <row r="70">
@@ -837,7 +835,7 @@
         <v>0.47808629274368286</v>
       </c>
       <c r="C70" s="1">
-        <v>-0.039584152400493622</v>
+        <v>-0.17810048162937164</v>
       </c>
     </row>
     <row r="71">
@@ -848,7 +846,7 @@
         <v>-0.081098131835460663</v>
       </c>
       <c r="C71" s="1">
-        <v>0.31023305654525757</v>
+        <v>0.28622972965240479</v>
       </c>
     </row>
     <row r="72">
@@ -859,7 +857,7 @@
         <v>-0.14883673191070557</v>
       </c>
       <c r="C72" s="1">
-        <v>0.11286122351884842</v>
+        <v>0.08901098370552063</v>
       </c>
     </row>
     <row r="73">
@@ -870,7 +868,7 @@
         <v>-0.29340636730194092</v>
       </c>
       <c r="C73" s="1">
-        <v>0.19620871543884277</v>
+        <v>0.18902665376663208</v>
       </c>
     </row>
     <row r="74">
@@ -881,7 +879,7 @@
         <v>-0.085644342005252838</v>
       </c>
       <c r="C74" s="1">
-        <v>0.17407107353210449</v>
+        <v>-0.31839153170585632</v>
       </c>
     </row>
     <row r="75">
@@ -892,7 +890,7 @@
         <v>-0.23748791217803955</v>
       </c>
       <c r="C75" s="1">
-        <v>0.29048082232475281</v>
+        <v>0.23552587628364563</v>
       </c>
     </row>
     <row r="76">
@@ -903,7 +901,7 @@
         <v>-0.27431225776672363</v>
       </c>
       <c r="C76" s="1">
-        <v>0.20553171634674072</v>
+        <v>-0.097134657204151154</v>
       </c>
     </row>
     <row r="77">
@@ -914,7 +912,7 @@
         <v>-0.081552751362323761</v>
       </c>
       <c r="C77" s="1">
-        <v>0.12987615168094635</v>
+        <v>0.10643484443426132</v>
       </c>
     </row>
     <row r="78">
@@ -925,7 +923,7 @@
         <v>-0.5343557596206665</v>
       </c>
       <c r="C78" s="1">
-        <v>0.47077649831771851</v>
+        <v>0.55929923057556152</v>
       </c>
     </row>
     <row r="79">
@@ -936,7 +934,7 @@
         <v>0.073473177850246429</v>
       </c>
       <c r="C79" s="1">
-        <v>0.12388721853494644</v>
+        <v>0.011222107335925102</v>
       </c>
     </row>
     <row r="80">
@@ -947,7 +945,7 @@
         <v>0.68357515335083008</v>
       </c>
       <c r="C80" s="1">
-        <v>0.24756355583667755</v>
+        <v>0.08033287525177002</v>
       </c>
     </row>
     <row r="81">
@@ -958,7 +956,7 @@
         <v>0.022555571049451828</v>
       </c>
       <c r="C81" s="1">
-        <v>-0.86706453561782837</v>
+        <v>-0.53040945529937744</v>
       </c>
     </row>
     <row r="82">
@@ -969,7 +967,7 @@
         <v>-0.4170633852481842</v>
       </c>
       <c r="C82" s="1">
-        <v>0.89609366655349731</v>
+        <v>0.80226534605026245</v>
       </c>
     </row>
     <row r="83">
@@ -980,7 +978,7 @@
         <v>0.40080064535140991</v>
       </c>
       <c r="C83" s="1">
-        <v>-0.168212890625</v>
+        <v>-0.17350739240646362</v>
       </c>
     </row>
     <row r="84">
@@ -991,7 +989,7 @@
         <v>-0.024725068360567093</v>
       </c>
       <c r="C84" s="1">
-        <v>0.23362226784229279</v>
+        <v>0.24075044691562653</v>
       </c>
     </row>
     <row r="85">
@@ -1002,7 +1000,7 @@
         <v>-0.32750296592712402</v>
       </c>
       <c r="C85" s="1">
-        <v>0.17369635403156281</v>
+        <v>0.19733011722564697</v>
       </c>
     </row>
     <row r="86">
@@ -1013,7 +1011,7 @@
         <v>0.016645489260554314</v>
       </c>
       <c r="C86" s="1">
-        <v>0.25243532657623291</v>
+        <v>-0.2870250940322876</v>
       </c>
     </row>
     <row r="87">
@@ -1024,7 +1022,7 @@
         <v>-0.33477693796157837</v>
       </c>
       <c r="C87" s="1">
-        <v>0.17556263506412506</v>
+        <v>0.16962769627571106</v>
       </c>
     </row>
     <row r="88">
@@ -1035,7 +1033,7 @@
         <v>-0.49389445781707764</v>
       </c>
       <c r="C88" s="1">
-        <v>0.26752117276191711</v>
+        <v>0.026722883805632591</v>
       </c>
     </row>
     <row r="89">
@@ -1046,7 +1044,7 @@
         <v>0.23486381769180298</v>
       </c>
       <c r="C89" s="1">
-        <v>0.16564086079597473</v>
+        <v>0.21062129735946655</v>
       </c>
     </row>
     <row r="90">
@@ -1057,7 +1055,7 @@
         <v>0.041649665683507919</v>
       </c>
       <c r="C90" s="1">
-        <v>-0.18208853900432587</v>
+        <v>-0.19942925870418549</v>
       </c>
     </row>
     <row r="91">
@@ -1068,7 +1066,7 @@
         <v>-0.44388607144355774</v>
       </c>
       <c r="C91" s="1">
-        <v>0.32209128141403198</v>
+        <v>0.29540929198265076</v>
       </c>
     </row>
     <row r="92">
@@ -1079,7 +1077,7 @@
         <v>-0.034726738929748535</v>
       </c>
       <c r="C92" s="1">
-        <v>0.2411031574010849</v>
+        <v>0.032848719507455826</v>
       </c>
     </row>
     <row r="93">
@@ -1090,7 +1088,7 @@
         <v>0.19349326193332672</v>
       </c>
       <c r="C93" s="1">
-        <v>-0.10738535225391388</v>
+        <v>0.33156019449234009</v>
       </c>
     </row>
     <row r="94">
@@ -1101,7 +1099,7 @@
         <v>-0.26431059837341309</v>
       </c>
       <c r="C94" s="1">
-        <v>0.1491856575012207</v>
+        <v>0.1113618016242981</v>
       </c>
     </row>
     <row r="95">
@@ -1112,7 +1110,7 @@
         <v>0.11575297266244888</v>
       </c>
       <c r="C95" s="1">
-        <v>0.060077112168073654</v>
+        <v>0.02762506902217865</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1121,7 @@
         <v>-0.28158619999885559</v>
       </c>
       <c r="C96" s="1">
-        <v>0.53723448514938354</v>
+        <v>0.55354487895965576</v>
       </c>
     </row>
     <row r="97">
@@ -1134,7 +1132,7 @@
         <v>0.15030419826507568</v>
       </c>
       <c r="C97" s="1">
-        <v>0.13752253353595734</v>
+        <v>0.079088583588600159</v>
       </c>
     </row>
     <row r="98">
@@ -1145,7 +1143,7 @@
         <v>0.53218626976013184</v>
       </c>
       <c r="C98" s="1">
-        <v>0.019076308235526085</v>
+        <v>-0.21660587191581726</v>
       </c>
     </row>
     <row r="99">
@@ -1156,7 +1154,7 @@
         <v>0.37534183263778687</v>
       </c>
       <c r="C99" s="1">
-        <v>0.27911442518234253</v>
+        <v>0.28248000144958496</v>
       </c>
     </row>
     <row r="100">
@@ -1167,7 +1165,7 @@
         <v>0.12393616139888763</v>
       </c>
       <c r="C100" s="1">
-        <v>-0.03558117151260376</v>
+        <v>-0.15702204406261444</v>
       </c>
     </row>
     <row r="101">
@@ -1178,7 +1176,7 @@
         <v>0.85314905643463135</v>
       </c>
       <c r="C101" s="1">
-        <v>0.44971445202827454</v>
+        <v>0.50214898586273193</v>
       </c>
     </row>
     <row r="102">
@@ -1189,7 +1187,7 @@
         <v>-0.058821678161621094</v>
       </c>
       <c r="C102" s="1">
-        <v>-0.072277873754501343</v>
+        <v>-0.057341206818819046</v>
       </c>
     </row>
     <row r="103">
@@ -1200,7 +1198,7 @@
         <v>0.15757815539836884</v>
       </c>
       <c r="C103" s="1">
-        <v>0.24413216114044189</v>
+        <v>0.26267528533935547</v>
       </c>
     </row>
     <row r="104">
@@ -1211,7 +1209,7 @@
         <v>0.48081403970718384</v>
       </c>
       <c r="C104" s="1">
-        <v>0.16561777889728546</v>
+        <v>0.11169304698705673</v>
       </c>
     </row>
     <row r="105">
@@ -1222,7 +1220,7 @@
         <v>0.044377397745847702</v>
       </c>
       <c r="C105" s="1">
-        <v>0.088611610233783722</v>
+        <v>0.24909408390522003</v>
       </c>
     </row>
     <row r="106">
@@ -1233,7 +1231,7 @@
         <v>0.026192536577582359</v>
       </c>
       <c r="C106" s="1">
-        <v>0.1574988067150116</v>
+        <v>0.032970573753118515</v>
       </c>
     </row>
     <row r="107">
@@ -1244,7 +1242,7 @@
         <v>-0.2615828812122345</v>
       </c>
       <c r="C107" s="1">
-        <v>0.22125604748725891</v>
+        <v>0.19191782176494598</v>
       </c>
     </row>
     <row r="108">
@@ -1255,7 +1253,7 @@
         <v>0.096658863127231598</v>
       </c>
       <c r="C108" s="1">
-        <v>0.12271932512521744</v>
+        <v>0.18382905423641205</v>
       </c>
     </row>
     <row r="109">
@@ -1263,10 +1261,10 @@
         <v>198312</v>
       </c>
       <c r="B109" s="1">
-        <v>0.22577138245105743</v>
+        <v>0.22577138245105744</v>
       </c>
       <c r="C109" s="1">
-        <v>0.25677520036697388</v>
+        <v>0.29407033324241638</v>
       </c>
     </row>
     <row r="110">
@@ -1277,7 +1275,7 @@
         <v>0.58765006065368652</v>
       </c>
       <c r="C110" s="1">
-        <v>0.21362452208995819</v>
+        <v>0.18246825039386749</v>
       </c>
     </row>
     <row r="111">
@@ -1288,7 +1286,7 @@
         <v>-0.070641838014125824</v>
       </c>
       <c r="C111" s="1">
-        <v>-0.063612617552280426</v>
+        <v>-0.11862593144178391</v>
       </c>
     </row>
     <row r="112">
@@ -1296,10 +1294,10 @@
         <v>198403</v>
       </c>
       <c r="B112" s="1">
-        <v>0.16939829289913177</v>
+        <v>0.16939829289913178</v>
       </c>
       <c r="C112" s="1">
-        <v>0.094509206712245941</v>
+        <v>-0.09972420334815979</v>
       </c>
     </row>
     <row r="113">
@@ -1310,7 +1308,7 @@
         <v>0.36624941229820251</v>
       </c>
       <c r="C113" s="1">
-        <v>0.10779804736375809</v>
+        <v>0.1117776483297348</v>
       </c>
     </row>
     <row r="114">
@@ -1321,7 +1319,7 @@
         <v>-0.17975097894668579</v>
       </c>
       <c r="C114" s="1">
-        <v>0.14094051718711853</v>
+        <v>0.5637810230255127</v>
       </c>
     </row>
     <row r="115">
@@ -1332,7 +1330,7 @@
         <v>-0.66437751054763794</v>
       </c>
       <c r="C115" s="1">
-        <v>0.11382832378149033</v>
+        <v>0.099918469786643982</v>
       </c>
     </row>
     <row r="116">
@@ -1343,7 +1341,7 @@
         <v>0.050742097198963165</v>
       </c>
       <c r="C116" s="1">
-        <v>0.15513400733470917</v>
+        <v>0.20938700437545776</v>
       </c>
     </row>
     <row r="117">
@@ -1354,7 +1352,7 @@
         <v>0.42671403288841248</v>
       </c>
       <c r="C117" s="1">
-        <v>-0.10545986890792847</v>
+        <v>0.28140568733215332</v>
       </c>
     </row>
     <row r="118">
@@ -1365,7 +1363,7 @@
         <v>-0.18793417513370514</v>
       </c>
       <c r="C118" s="1">
-        <v>0.3993602991104126</v>
+        <v>0.40459084510803223</v>
       </c>
     </row>
     <row r="119">
@@ -1376,7 +1374,7 @@
         <v>0.11984456330537796</v>
       </c>
       <c r="C119" s="1">
-        <v>0.14274886250495911</v>
+        <v>0.1722637265920639</v>
       </c>
     </row>
     <row r="120">
@@ -1387,7 +1385,7 @@
         <v>-0.26749294996261597</v>
       </c>
       <c r="C120" s="1">
-        <v>0.16813105344772339</v>
+        <v>0.18348896503448486</v>
       </c>
     </row>
     <row r="121">
@@ -1398,7 +1396,7 @@
         <v>-0.014268770813941956</v>
       </c>
       <c r="C121" s="1">
-        <v>0.12567080557346344</v>
+        <v>0.15544959902763367</v>
       </c>
     </row>
     <row r="122">
@@ -1409,7 +1407,7 @@
         <v>0.59674245119094849</v>
       </c>
       <c r="C122" s="1">
-        <v>0.17607462406158447</v>
+        <v>0.15495069324970245</v>
       </c>
     </row>
     <row r="123">
@@ -1420,7 +1418,7 @@
         <v>-0.19020728766918182</v>
       </c>
       <c r="C123" s="1">
-        <v>0.26924261450767517</v>
+        <v>0.35758844017982483</v>
       </c>
     </row>
     <row r="124">
@@ -1431,7 +1429,7 @@
         <v>-0.2979525625705719</v>
       </c>
       <c r="C124" s="1">
-        <v>0.24899640679359436</v>
+        <v>0.10647492110729218</v>
       </c>
     </row>
     <row r="125">
@@ -1442,7 +1440,7 @@
         <v>0.28850910067558289</v>
       </c>
       <c r="C125" s="1">
-        <v>-0.075689978897571564</v>
+        <v>-0.17026309669017792</v>
       </c>
     </row>
     <row r="126">
@@ -1453,7 +1451,7 @@
         <v>0.025283295661211014</v>
       </c>
       <c r="C126" s="1">
-        <v>0.1401083916425705</v>
+        <v>0.18688380718231201</v>
       </c>
     </row>
     <row r="127">
@@ -1461,10 +1459,10 @@
         <v>198506</v>
       </c>
       <c r="B127" s="1">
-        <v>-0.33250382542610168</v>
+        <v>-0.33250382542610169</v>
       </c>
       <c r="C127" s="1">
-        <v>-0.080533452332019806</v>
+        <v>-0.16762737929821014</v>
       </c>
     </row>
     <row r="128">
@@ -1475,7 +1473,7 @@
         <v>0.29760155081748962</v>
       </c>
       <c r="C128" s="1">
-        <v>0.35476899147033691</v>
+        <v>0.31093728542327881</v>
       </c>
     </row>
     <row r="129">
@@ -1486,7 +1484,7 @@
         <v>-0.0042671025730669498</v>
       </c>
       <c r="C129" s="1">
-        <v>0.079380162060260773</v>
+        <v>0.22185327112674713</v>
       </c>
     </row>
     <row r="130">
@@ -1497,7 +1495,7 @@
         <v>0.20622263848781586</v>
       </c>
       <c r="C130" s="1">
-        <v>0.09351079910993576</v>
+        <v>-0.034199174493551254</v>
       </c>
     </row>
     <row r="131">
@@ -1508,7 +1506,7 @@
         <v>0.60992652177810669</v>
       </c>
       <c r="C131" s="1">
-        <v>0.0075663821771740913</v>
+        <v>-0.022703811526298523</v>
       </c>
     </row>
     <row r="132">
@@ -1519,7 +1517,7 @@
         <v>0.038921941071748734</v>
       </c>
       <c r="C132" s="1">
-        <v>0.13269501924514771</v>
+        <v>0.15564741194248199</v>
       </c>
     </row>
     <row r="133">
@@ -1530,7 +1528,7 @@
         <v>-0.13701656460762024</v>
       </c>
       <c r="C133" s="1">
-        <v>0.15041482448577881</v>
+        <v>0.12483949214220047</v>
       </c>
     </row>
     <row r="134">
@@ -1541,7 +1539,7 @@
         <v>-0.24203413724899292</v>
       </c>
       <c r="C134" s="1">
-        <v>0.10617362707853317</v>
+        <v>-0.008258327841758728</v>
       </c>
     </row>
     <row r="135">
@@ -1552,7 +1550,7 @@
         <v>-0.20384594798088074</v>
       </c>
       <c r="C135" s="1">
-        <v>0.13733105361461639</v>
+        <v>0.086900182068347931</v>
       </c>
     </row>
     <row r="136">
@@ -1563,7 +1561,7 @@
         <v>-0.13156111538410187</v>
       </c>
       <c r="C136" s="1">
-        <v>0.12005840986967087</v>
+        <v>0.045806143432855606</v>
       </c>
     </row>
     <row r="137">
@@ -1574,7 +1572,7 @@
         <v>-0.28704166412353516</v>
       </c>
       <c r="C137" s="1">
-        <v>-1.2989181280136108</v>
+        <v>-1.443103551864624</v>
       </c>
     </row>
     <row r="138">
@@ -1585,7 +1583,7 @@
         <v>0.30623936653137207</v>
       </c>
       <c r="C138" s="1">
-        <v>2.0361075401306152</v>
+        <v>2.2610416412353516</v>
       </c>
     </row>
     <row r="139">
@@ -1596,7 +1594,7 @@
         <v>0.17121678590774536</v>
       </c>
       <c r="C139" s="1">
-        <v>0.51592820882797241</v>
+        <v>0.31500503420829773</v>
       </c>
     </row>
     <row r="140">
@@ -1607,7 +1605,7 @@
         <v>-0.54708516597747803</v>
       </c>
       <c r="C140" s="1">
-        <v>0.30901995301246643</v>
+        <v>0.16532999277114868</v>
       </c>
     </row>
     <row r="141">
@@ -1618,7 +1616,7 @@
         <v>0.50809133052825928</v>
       </c>
       <c r="C141" s="1">
-        <v>0.13616213202476501</v>
+        <v>0.16513326764106751</v>
       </c>
     </row>
     <row r="142">
@@ -1629,7 +1627,7 @@
         <v>-0.10064685344696045</v>
       </c>
       <c r="C142" s="1">
-        <v>-0.32672375440597534</v>
+        <v>-0.57239717245101929</v>
       </c>
     </row>
     <row r="143">
@@ -1640,7 +1638,7 @@
         <v>0.040740422904491425</v>
       </c>
       <c r="C143" s="1">
-        <v>0.28812146186828613</v>
+        <v>0.30342227220535278</v>
       </c>
     </row>
     <row r="144">
@@ -1651,7 +1649,7 @@
         <v>0.078474000096321106</v>
       </c>
       <c r="C144" s="1">
-        <v>0.24691139161586761</v>
+        <v>0.29043695330619812</v>
       </c>
     </row>
     <row r="145">
@@ -1662,7 +1660,7 @@
         <v>-0.25612741708755493</v>
       </c>
       <c r="C145" s="1">
-        <v>0.32753682136535645</v>
+        <v>0.33962538838386536</v>
       </c>
     </row>
     <row r="146">
@@ -1673,7 +1671,7 @@
         <v>0.10529668629169464</v>
       </c>
       <c r="C146" s="1">
-        <v>0.13456149399280548</v>
+        <v>-0.12443556636571884</v>
       </c>
     </row>
     <row r="147">
@@ -1684,7 +1682,7 @@
         <v>0.16985292732715607</v>
       </c>
       <c r="C147" s="1">
-        <v>-0.11464482545852661</v>
+        <v>-0.27569690346717834</v>
       </c>
     </row>
     <row r="148">
@@ -1695,7 +1693,7 @@
         <v>0.1980394572019577</v>
       </c>
       <c r="C148" s="1">
-        <v>0.050983399152755737</v>
+        <v>-0.083467938005924225</v>
       </c>
     </row>
     <row r="149">
@@ -1706,7 +1704,7 @@
         <v>0.28305366635322571</v>
       </c>
       <c r="C149" s="1">
-        <v>0.056614488363265991</v>
+        <v>0.030667882412672043</v>
       </c>
     </row>
     <row r="150">
@@ -1717,7 +1715,7 @@
         <v>0.025283295661211014</v>
       </c>
       <c r="C150" s="1">
-        <v>0.20356443524360657</v>
+        <v>0.23192977905273438</v>
       </c>
     </row>
     <row r="151">
@@ -1728,7 +1726,7 @@
         <v>0.072563931345939636</v>
       </c>
       <c r="C151" s="1">
-        <v>-0.11373407393693924</v>
+        <v>-0.15178336203098297</v>
       </c>
     </row>
     <row r="152">
@@ -1739,7 +1737,7 @@
         <v>0.57264751195907593</v>
       </c>
       <c r="C152" s="1">
-        <v>0.28227806091308594</v>
+        <v>0.35121777653694153</v>
       </c>
     </row>
     <row r="153">
@@ -1750,7 +1748,7 @@
         <v>0.35124689340591431</v>
       </c>
       <c r="C153" s="1">
-        <v>-0.34745761752128601</v>
+        <v>-0.3242400586605072</v>
       </c>
     </row>
     <row r="154">
@@ -1761,7 +1759,7 @@
         <v>0.11620759963989258</v>
       </c>
       <c r="C154" s="1">
-        <v>0.6094813346862793</v>
+        <v>0.42720997333526611</v>
       </c>
     </row>
     <row r="155">
@@ -1772,7 +1770,7 @@
         <v>-1.3467643260955811</v>
       </c>
       <c r="C155" s="1">
-        <v>0.33501124382019043</v>
+        <v>0.38441190123558044</v>
       </c>
     </row>
     <row r="156">
@@ -1783,7 +1781,7 @@
         <v>-0.96124535799026489</v>
       </c>
       <c r="C156" s="1">
-        <v>0.15802542865276337</v>
+        <v>0.16062755882740021</v>
       </c>
     </row>
     <row r="157">
@@ -1794,7 +1792,7 @@
         <v>-0.08518972247838974</v>
       </c>
       <c r="C157" s="1">
-        <v>0.1423213928937912</v>
+        <v>0.14245988428592682</v>
       </c>
     </row>
     <row r="158">
@@ -1805,7 +1803,7 @@
         <v>0.0084622986614704132</v>
       </c>
       <c r="C158" s="1">
-        <v>0.13578195869922638</v>
+        <v>-0.050323687493801117</v>
       </c>
     </row>
     <row r="159">
@@ -1816,7 +1814,7 @@
         <v>0.28669062256813049</v>
       </c>
       <c r="C159" s="1">
-        <v>0.14782726764678955</v>
+        <v>0.1361708790063858</v>
       </c>
     </row>
     <row r="160">
@@ -1827,7 +1825,7 @@
         <v>0.45126360654830933</v>
       </c>
       <c r="C160" s="1">
-        <v>0.0078766914084553719</v>
+        <v>-0.22825388610363007</v>
       </c>
     </row>
     <row r="161">
@@ -1838,7 +1836,7 @@
         <v>0.0052799535915255547</v>
       </c>
       <c r="C161" s="1">
-        <v>0.18500968813896179</v>
+        <v>0.2113506942987442</v>
       </c>
     </row>
     <row r="162">
@@ -1849,7 +1847,7 @@
         <v>-0.26067361235618591</v>
       </c>
       <c r="C162" s="1">
-        <v>0.00056232366478070617</v>
+        <v>0.033886827528476715</v>
       </c>
     </row>
     <row r="163">
@@ -1860,7 +1858,7 @@
         <v>0.29032763838768005</v>
       </c>
       <c r="C163" s="1">
-        <v>0.077692747116088867</v>
+        <v>0.092514857649803162</v>
       </c>
     </row>
     <row r="164">
@@ -1871,7 +1869,7 @@
         <v>-0.017905747517943382</v>
       </c>
       <c r="C164" s="1">
-        <v>-0.0069799860939383507</v>
+        <v>0.43622565269470215</v>
       </c>
     </row>
     <row r="165">
@@ -1882,7 +1880,7 @@
         <v>-0.45570623874664307</v>
       </c>
       <c r="C165" s="1">
-        <v>0.01344390120357275</v>
+        <v>0.42402383685112</v>
       </c>
     </row>
     <row r="166">
@@ -1893,7 +1891,7 @@
         <v>0.1466672271490097</v>
       </c>
       <c r="C166" s="1">
-        <v>0.41731944680213928</v>
+        <v>0.27047872543334961</v>
       </c>
     </row>
     <row r="167">
@@ -1904,7 +1902,7 @@
         <v>0.0098261693492531776</v>
       </c>
       <c r="C167" s="1">
-        <v>-0.2827906608581543</v>
+        <v>0.047127146273851395</v>
       </c>
     </row>
     <row r="168">
@@ -1915,7 +1913,7 @@
         <v>0.16667057573795319</v>
       </c>
       <c r="C168" s="1">
-        <v>-0.15692247450351715</v>
+        <v>0.17682681977748871</v>
       </c>
     </row>
     <row r="169">
@@ -1926,7 +1924,7 @@
         <v>0.55082577466964722</v>
       </c>
       <c r="C169" s="1">
-        <v>-0.22655875980854034</v>
+        <v>0.12896102666854858</v>
       </c>
     </row>
     <row r="170">
@@ -1937,7 +1935,7 @@
         <v>0.67311888933181763</v>
       </c>
       <c r="C170" s="1">
-        <v>0.14924725890159607</v>
+        <v>0.12716153264045715</v>
       </c>
     </row>
     <row r="171">
@@ -1948,7 +1946,7 @@
         <v>0.047105129808187485</v>
       </c>
       <c r="C171" s="1">
-        <v>-0.12906821072101593</v>
+        <v>-0.12120270729064941</v>
       </c>
     </row>
     <row r="172">
@@ -1959,7 +1957,7 @@
         <v>0.46899387240409851</v>
       </c>
       <c r="C172" s="1">
-        <v>-0.32813110947608948</v>
+        <v>-0.43033808469772339</v>
       </c>
     </row>
     <row r="173">
@@ -1970,7 +1968,7 @@
         <v>0.27532508969306946</v>
       </c>
       <c r="C173" s="1">
-        <v>-0.11985356360673904</v>
+        <v>-0.15127219259738922</v>
       </c>
     </row>
     <row r="174">
@@ -1981,7 +1979,7 @@
         <v>-0.062458649277687073</v>
       </c>
       <c r="C174" s="1">
-        <v>-0.41128507256507874</v>
+        <v>-0.38400277495384216</v>
       </c>
     </row>
     <row r="175">
@@ -1992,7 +1990,7 @@
         <v>-0.075642675161361694</v>
       </c>
       <c r="C175" s="1">
-        <v>-0.29743403196334839</v>
+        <v>-0.31209465861320496</v>
       </c>
     </row>
     <row r="176">
@@ -2003,7 +2001,7 @@
         <v>-0.019269609823822975</v>
       </c>
       <c r="C176" s="1">
-        <v>0.23584119975566864</v>
+        <v>0.269386887550354</v>
       </c>
     </row>
     <row r="177">
@@ -2014,7 +2012,7 @@
         <v>0.15530504286289215</v>
       </c>
       <c r="C177" s="1">
-        <v>-0.23127906024456024</v>
+        <v>-0.041072674095630646</v>
       </c>
     </row>
     <row r="178">
@@ -2025,7 +2023,7 @@
         <v>-0.036999847739934921</v>
       </c>
       <c r="C178" s="1">
-        <v>-0.17006295919418335</v>
+        <v>-0.27824997901916504</v>
       </c>
     </row>
     <row r="179">
@@ -2036,7 +2034,7 @@
         <v>-0.59891200065612793</v>
       </c>
       <c r="C179" s="1">
-        <v>0.25132480263710022</v>
+        <v>0.29121965169906616</v>
       </c>
     </row>
     <row r="180">
@@ -2047,7 +2045,7 @@
         <v>0.23986463248729706</v>
       </c>
       <c r="C180" s="1">
-        <v>0.25643759965896606</v>
+        <v>0.061634115874767304</v>
       </c>
     </row>
     <row r="181">
@@ -2055,10 +2053,10 @@
         <v>198912</v>
       </c>
       <c r="B181" s="1">
-        <v>0.35670232772827148</v>
+        <v>0.35670232772827149</v>
       </c>
       <c r="C181" s="1">
-        <v>0.45816811919212341</v>
+        <v>0.24955111742019653</v>
       </c>
     </row>
     <row r="182">
@@ -2069,7 +2067,7 @@
         <v>0.36761325597763062</v>
       </c>
       <c r="C182" s="1">
-        <v>0.09900481253862381</v>
+        <v>0.01340863760560751</v>
       </c>
     </row>
     <row r="183">
@@ -2080,7 +2078,7 @@
         <v>0.27305203676223755</v>
       </c>
       <c r="C183" s="1">
-        <v>-0.02806362509727478</v>
+        <v>-0.021446892991662026</v>
       </c>
     </row>
     <row r="184">
@@ -2091,7 +2089,7 @@
         <v>0.037558071315288544</v>
       </c>
       <c r="C184" s="1">
-        <v>-0.24254760146141052</v>
+        <v>-0.43525522947311401</v>
       </c>
     </row>
     <row r="185">
@@ -2102,7 +2100,7 @@
         <v>-0.36069035530090332</v>
       </c>
       <c r="C185" s="1">
-        <v>0.31615981459617615</v>
+        <v>0.12379167228937149</v>
       </c>
     </row>
     <row r="186">
@@ -2113,7 +2111,7 @@
         <v>0.37352335453033447</v>
       </c>
       <c r="C186" s="1">
-        <v>-0.04027886688709259</v>
+        <v>0.02024463564157486</v>
       </c>
     </row>
     <row r="187">
@@ -2124,7 +2122,7 @@
         <v>-0.23430557548999786</v>
       </c>
       <c r="C187" s="1">
-        <v>-0.1124403178691864</v>
+        <v>-0.08919912576675415</v>
       </c>
     </row>
     <row r="188">
@@ -2135,7 +2133,7 @@
         <v>0.34260910749435425</v>
       </c>
       <c r="C188" s="1">
-        <v>0.31590384244918823</v>
+        <v>0.31006607413291931</v>
       </c>
     </row>
     <row r="189">
@@ -2146,7 +2144,7 @@
         <v>-0.29840719699859619</v>
       </c>
       <c r="C189" s="1">
-        <v>0.086368776857852936</v>
+        <v>0.25461903214454651</v>
       </c>
     </row>
     <row r="190">
@@ -2157,7 +2155,7 @@
         <v>-0.42751970887184143</v>
       </c>
       <c r="C190" s="1">
-        <v>0.02446245402097702</v>
+        <v>-0.13438133895397186</v>
       </c>
     </row>
     <row r="191">
@@ -2168,7 +2166,7 @@
         <v>-0.42751970887184143</v>
       </c>
       <c r="C191" s="1">
-        <v>0.21224090456962585</v>
+        <v>0.098919868469238281</v>
       </c>
     </row>
     <row r="192">
@@ -2179,7 +2177,7 @@
         <v>-0.16884006559848785</v>
       </c>
       <c r="C192" s="1">
-        <v>0.40381726622581482</v>
+        <v>0.20974060893058777</v>
       </c>
     </row>
     <row r="193">
@@ -2190,7 +2188,7 @@
         <v>-0.3493247926235199</v>
       </c>
       <c r="C193" s="1">
-        <v>-0.061793282628059387</v>
+        <v>0.11047327518463135</v>
       </c>
     </row>
     <row r="194">
@@ -2201,7 +2199,7 @@
         <v>-0.40797096490859985</v>
       </c>
       <c r="C194" s="1">
-        <v>-0.13448674976825714</v>
+        <v>-0.15048409998416901</v>
       </c>
     </row>
     <row r="195">
@@ -2212,7 +2210,7 @@
         <v>0.53264087438583374</v>
       </c>
       <c r="C195" s="1">
-        <v>0.0056434781290590763</v>
+        <v>0.014835824258625507</v>
       </c>
     </row>
     <row r="196">
@@ -2223,7 +2221,7 @@
         <v>0.12802775204181671</v>
       </c>
       <c r="C196" s="1">
-        <v>-0.85785770416259766</v>
+        <v>-0.88649630546569824</v>
       </c>
     </row>
     <row r="197">
@@ -2234,7 +2232,7 @@
         <v>-0.17247705161571503</v>
       </c>
       <c r="C197" s="1">
-        <v>-0.60379970073699951</v>
+        <v>-0.56224632263183594</v>
       </c>
     </row>
     <row r="198">
@@ -2242,10 +2240,10 @@
         <v>199105</v>
       </c>
       <c r="B198" s="1">
-        <v>0.35670232772827148</v>
+        <v>0.35670232772827149</v>
       </c>
       <c r="C198" s="1">
-        <v>-0.30584117770195007</v>
+        <v>-0.23242360353469849</v>
       </c>
     </row>
     <row r="199">
@@ -2256,7 +2254,7 @@
         <v>-0.27931308746337891</v>
       </c>
       <c r="C199" s="1">
-        <v>-0.40161904692649841</v>
+        <v>-0.33515849709510803</v>
       </c>
     </row>
     <row r="200">
@@ -2267,7 +2265,7 @@
         <v>0.09211266040802002</v>
       </c>
       <c r="C200" s="1">
-        <v>0.22717007994651794</v>
+        <v>0.030426418408751488</v>
       </c>
     </row>
     <row r="201">
@@ -2278,7 +2276,7 @@
         <v>0.084838710725307465</v>
       </c>
       <c r="C201" s="1">
-        <v>0.5291629433631897</v>
+        <v>0.30762496590614319</v>
       </c>
     </row>
     <row r="202">
@@ -2289,7 +2287,7 @@
         <v>-0.36341807246208191</v>
       </c>
       <c r="C202" s="1">
-        <v>-0.015704313293099403</v>
+        <v>-0.038878947496414185</v>
       </c>
     </row>
     <row r="203">
@@ -2300,7 +2298,7 @@
         <v>-0.28113159537315369</v>
       </c>
       <c r="C203" s="1">
-        <v>0.35495629906654358</v>
+        <v>0.15229259431362152</v>
       </c>
     </row>
     <row r="204">
@@ -2311,7 +2309,7 @@
         <v>-0.84122520685195923</v>
       </c>
       <c r="C204" s="1">
-        <v>0.68334352970123291</v>
+        <v>0.48410290479660034</v>
       </c>
     </row>
     <row r="205">
@@ -2322,7 +2320,7 @@
         <v>0.17348991334438324</v>
       </c>
       <c r="C205" s="1">
-        <v>0.49914878606796265</v>
+        <v>0.3001401424407959</v>
       </c>
     </row>
     <row r="206">
@@ -2333,7 +2331,7 @@
         <v>0.30442088842391968</v>
       </c>
       <c r="C206" s="1">
-        <v>0.056260228157043457</v>
+        <v>-0.12028676271438599</v>
       </c>
     </row>
     <row r="207">
@@ -2344,7 +2342,7 @@
         <v>-0.42706510424613953</v>
       </c>
       <c r="C207" s="1">
-        <v>-0.23804599046707153</v>
+        <v>-0.21349644660949707</v>
       </c>
     </row>
     <row r="208">
@@ -2355,7 +2353,7 @@
         <v>0.28032594919204712</v>
       </c>
       <c r="C208" s="1">
-        <v>-0.4267246425151825</v>
+        <v>-0.50446522235870361</v>
       </c>
     </row>
     <row r="209">
@@ -2366,7 +2364,7 @@
         <v>0.19713021814823151</v>
       </c>
       <c r="C209" s="1">
-        <v>-0.039516497403383255</v>
+        <v>-0.020717525854706764</v>
       </c>
     </row>
     <row r="210">
@@ -2377,7 +2375,7 @@
         <v>0.075291655957698822</v>
       </c>
       <c r="C210" s="1">
-        <v>0.14177703857421875</v>
+        <v>0.17998500168323517</v>
       </c>
     </row>
     <row r="211">
@@ -2388,7 +2386,7 @@
         <v>-0.57481706142425537</v>
       </c>
       <c r="C211" s="1">
-        <v>0.25021132826805115</v>
+        <v>0.29856359958648682</v>
       </c>
     </row>
     <row r="212">
@@ -2399,7 +2397,7 @@
         <v>-0.30795425176620483</v>
       </c>
       <c r="C212" s="1">
-        <v>0.42178815603256226</v>
+        <v>0.45171248912811279</v>
       </c>
     </row>
     <row r="213">
@@ -2410,7 +2408,7 @@
         <v>-0.77485054731369019</v>
       </c>
       <c r="C213" s="1">
-        <v>0.23647554218769073</v>
+        <v>0.40706810355186463</v>
       </c>
     </row>
     <row r="214">
@@ -2421,7 +2419,7 @@
         <v>-0.020633475854992867</v>
       </c>
       <c r="C214" s="1">
-        <v>-0.17608724534511566</v>
+        <v>-0.19500619173049927</v>
       </c>
     </row>
     <row r="215">
@@ -2432,7 +2430,7 @@
         <v>0.14030253887176514</v>
       </c>
       <c r="C215" s="1">
-        <v>-0.49185213446617126</v>
+        <v>-0.42027226090431213</v>
       </c>
     </row>
     <row r="216">
@@ -2443,7 +2441,7 @@
         <v>0.1812184751033783</v>
       </c>
       <c r="C216" s="1">
-        <v>-0.51074099540710449</v>
+        <v>-0.66238093376159668</v>
       </c>
     </row>
     <row r="217">
@@ -2454,7 +2452,7 @@
         <v>0.11438909918069839</v>
       </c>
       <c r="C217" s="1">
-        <v>-0.16311803460121155</v>
+        <v>-0.32526892423629761</v>
       </c>
     </row>
     <row r="218">
@@ -2465,7 +2463,7 @@
         <v>0.056197553873062134</v>
       </c>
       <c r="C218" s="1">
-        <v>-0.28336489200592041</v>
+        <v>-0.27349081635475159</v>
       </c>
     </row>
     <row r="219">
@@ -2476,7 +2474,7 @@
         <v>0.027556406334042549</v>
       </c>
       <c r="C219" s="1">
-        <v>-0.29959937930107117</v>
+        <v>-0.25844356417655945</v>
       </c>
     </row>
     <row r="220">
@@ -2487,7 +2485,7 @@
         <v>0.37670570611953735</v>
       </c>
       <c r="C220" s="1">
-        <v>-0.23880335688591003</v>
+        <v>-0.35273346304893494</v>
       </c>
     </row>
     <row r="221">
@@ -2498,7 +2496,7 @@
         <v>0.10666053742170334</v>
       </c>
       <c r="C221" s="1">
-        <v>0.24175432324409485</v>
+        <v>0.27776762843132019</v>
       </c>
     </row>
     <row r="222">
@@ -2509,7 +2507,7 @@
         <v>-0.12519641220569611</v>
       </c>
       <c r="C222" s="1">
-        <v>0.18246647715568542</v>
+        <v>-0.0027783808764070272</v>
       </c>
     </row>
     <row r="223">
@@ -2520,7 +2518,7 @@
         <v>0.012553893961012363</v>
       </c>
       <c r="C223" s="1">
-        <v>-0.28294071555137634</v>
+        <v>-0.22873584926128387</v>
       </c>
     </row>
     <row r="224">
@@ -2531,7 +2529,7 @@
         <v>0.36897715926170349</v>
       </c>
       <c r="C224" s="1">
-        <v>-0.69728302955627441</v>
+        <v>-0.51558452844619751</v>
       </c>
     </row>
     <row r="225">
@@ -2542,7 +2540,7 @@
         <v>0.23577304184436798</v>
       </c>
       <c r="C225" s="1">
-        <v>-0.19916699826717377</v>
+        <v>-0.058608639985322952</v>
       </c>
     </row>
     <row r="226">
@@ -2553,7 +2551,7 @@
         <v>-0.25158116221427917</v>
       </c>
       <c r="C226" s="1">
-        <v>0.34680891036987305</v>
+        <v>0.3046291172504425</v>
       </c>
     </row>
     <row r="227">
@@ -2564,7 +2562,7 @@
         <v>0.56537359952926636</v>
       </c>
       <c r="C227" s="1">
-        <v>-0.041781123727560043</v>
+        <v>-0.21419674158096314</v>
       </c>
     </row>
     <row r="228">
@@ -2575,7 +2573,7 @@
         <v>-0.33932316303253174</v>
       </c>
       <c r="C228" s="1">
-        <v>-0.081728667020797729</v>
+        <v>-0.24792890250682831</v>
       </c>
     </row>
     <row r="229">
@@ -2586,7 +2584,7 @@
         <v>0.29487386345863342</v>
       </c>
       <c r="C229" s="1">
-        <v>-0.16377270221710205</v>
+        <v>-0.036544620990753174</v>
       </c>
     </row>
     <row r="230">
@@ -2597,7 +2595,7 @@
         <v>0.57401144504547119</v>
       </c>
       <c r="C230" s="1">
-        <v>-0.30526056885719299</v>
+        <v>-0.16265974938869476</v>
       </c>
     </row>
     <row r="231">
@@ -2608,7 +2606,7 @@
         <v>0.0016429796814918518</v>
       </c>
       <c r="C231" s="1">
-        <v>-0.084481768310070038</v>
+        <v>-0.061094019562005997</v>
       </c>
     </row>
     <row r="232">
@@ -2619,7 +2617,7 @@
         <v>-0.44661381840705872</v>
       </c>
       <c r="C232" s="1">
-        <v>0.23405507206916809</v>
+        <v>0.19384594261646271</v>
       </c>
     </row>
     <row r="233">
@@ -2630,7 +2628,7 @@
         <v>-0.046092275530099869</v>
       </c>
       <c r="C233" s="1">
-        <v>-0.086508557200431824</v>
+        <v>-0.02937161922454834</v>
       </c>
     </row>
     <row r="234">
@@ -2641,7 +2639,7 @@
         <v>-0.031089769676327705</v>
       </c>
       <c r="C234" s="1">
-        <v>0.41345185041427612</v>
+        <v>0.22345443069934845</v>
       </c>
     </row>
     <row r="235">
@@ -2652,7 +2650,7 @@
         <v>-0.34068700671195984</v>
       </c>
       <c r="C235" s="1">
-        <v>0.061242904514074326</v>
+        <v>0.088119804859161377</v>
       </c>
     </row>
     <row r="236">
@@ -2663,7 +2661,7 @@
         <v>0.47217622399330139</v>
       </c>
       <c r="C236" s="1">
-        <v>0.21767272055149078</v>
+        <v>0.23870635032653809</v>
       </c>
     </row>
     <row r="237">
@@ -2674,7 +2672,7 @@
         <v>-0.052002355456352234</v>
       </c>
       <c r="C237" s="1">
-        <v>0.30551421642303467</v>
+        <v>0.093305528163909912</v>
       </c>
     </row>
     <row r="238">
@@ -2685,7 +2683,7 @@
         <v>-0.42433732748031616</v>
       </c>
       <c r="C238" s="1">
-        <v>-0.070461392402648926</v>
+        <v>-0.093091681599617004</v>
       </c>
     </row>
     <row r="239">
@@ -2696,7 +2694,7 @@
         <v>0.044377397745847702</v>
       </c>
       <c r="C239" s="1">
-        <v>0.43902236223220825</v>
+        <v>0.24402585625648499</v>
       </c>
     </row>
     <row r="240">
@@ -2707,7 +2705,7 @@
         <v>0.072563931345939636</v>
       </c>
       <c r="C240" s="1">
-        <v>0.01526254415512085</v>
+        <v>-0.15843309462070465</v>
       </c>
     </row>
     <row r="241">
@@ -2718,7 +2716,7 @@
         <v>0.20985962450504303</v>
       </c>
       <c r="C241" s="1">
-        <v>-0.025480493903160095</v>
+        <v>-0.20148296654224396</v>
       </c>
     </row>
     <row r="242">
@@ -2729,7 +2727,7 @@
         <v>-0.068368732929229736</v>
       </c>
       <c r="C242" s="1">
-        <v>0.31877189874649048</v>
+        <v>0.21491384506225586</v>
       </c>
     </row>
     <row r="243">
@@ -2740,7 +2738,7 @@
         <v>-0.26931142807006836</v>
       </c>
       <c r="C243" s="1">
-        <v>0.1201978474855423</v>
+        <v>0.13333240151405334</v>
       </c>
     </row>
     <row r="244">
@@ -2751,7 +2749,7 @@
         <v>-0.31568282842636108</v>
       </c>
       <c r="C244" s="1">
-        <v>0.38346266746520996</v>
+        <v>0.31720253825187683</v>
       </c>
     </row>
     <row r="245">
@@ -2762,7 +2760,7 @@
         <v>0.37761494517326355</v>
       </c>
       <c r="C245" s="1">
-        <v>0.26297232508659363</v>
+        <v>0.068238839507102966</v>
       </c>
     </row>
     <row r="246">
@@ -2773,7 +2771,7 @@
         <v>-0.048365384340286255</v>
       </c>
       <c r="C246" s="1">
-        <v>-0.25427374243736267</v>
+        <v>-0.18275845050811768</v>
       </c>
     </row>
     <row r="247">
@@ -2784,7 +2782,7 @@
         <v>0.037558071315288544</v>
       </c>
       <c r="C247" s="1">
-        <v>0.062260277569293976</v>
+        <v>0.064072199165821076</v>
       </c>
     </row>
     <row r="248">
@@ -2795,7 +2793,7 @@
         <v>0.12029919028282166</v>
       </c>
       <c r="C248" s="1">
-        <v>-0.08492230623960495</v>
+        <v>0.057410035282373428</v>
       </c>
     </row>
     <row r="249">
@@ -2806,7 +2804,7 @@
         <v>-0.084735102951526642</v>
       </c>
       <c r="C249" s="1">
-        <v>-0.29368498921394348</v>
+        <v>-0.15739579498767853</v>
       </c>
     </row>
     <row r="250">
@@ -2817,7 +2815,7 @@
         <v>-0.02699817530810833</v>
       </c>
       <c r="C250" s="1">
-        <v>-0.24581702053546906</v>
+        <v>-0.27608981728553772</v>
       </c>
     </row>
     <row r="251">
@@ -2828,7 +2826,7 @@
         <v>-0.30749961733818054</v>
       </c>
       <c r="C251" s="1">
-        <v>0.50934362411499023</v>
+        <v>0.30601617693901062</v>
       </c>
     </row>
     <row r="252">
@@ -2839,7 +2837,7 @@
         <v>0.033921103924512863</v>
       </c>
       <c r="C252" s="1">
-        <v>-0.12369462102651596</v>
+        <v>0.011621041223406792</v>
       </c>
     </row>
     <row r="253">
@@ -2850,7 +2848,7 @@
         <v>0.033921103924512863</v>
       </c>
       <c r="C253" s="1">
-        <v>0.023300938308238983</v>
+        <v>-0.15135481953620911</v>
       </c>
     </row>
     <row r="254">
@@ -2861,7 +2859,7 @@
         <v>0.0057345745153725147</v>
       </c>
       <c r="C254" s="1">
-        <v>-0.22781883180141449</v>
+        <v>-0.012679296545684338</v>
       </c>
     </row>
     <row r="255">
@@ -2869,10 +2867,10 @@
         <v>199602</v>
       </c>
       <c r="B255" s="1">
-        <v>0.06983620673418045</v>
+        <v>0.069836206734180451</v>
       </c>
       <c r="C255" s="1">
-        <v>-0.10025802254676819</v>
+        <v>-0.032855693250894547</v>
       </c>
     </row>
     <row r="256">
@@ -2883,7 +2881,7 @@
         <v>0.0034614624455571175</v>
       </c>
       <c r="C256" s="1">
-        <v>-0.047667872160673141</v>
+        <v>-0.076220743358135223</v>
       </c>
     </row>
     <row r="257">
@@ -2894,7 +2892,7 @@
         <v>0.31124019622802734</v>
       </c>
       <c r="C257" s="1">
-        <v>-0.24261064827442169</v>
+        <v>-0.21168103814125061</v>
       </c>
     </row>
     <row r="258">
@@ -2905,7 +2903,7 @@
         <v>-0.049729250371456146</v>
       </c>
       <c r="C258" s="1">
-        <v>-0.1908290684223175</v>
+        <v>-0.13361835479736328</v>
       </c>
     </row>
     <row r="259">
@@ -2916,7 +2914,7 @@
         <v>-0.077461160719394684</v>
       </c>
       <c r="C259" s="1">
-        <v>-0.072885200381278992</v>
+        <v>-0.00078226713230833411</v>
       </c>
     </row>
     <row r="260">
@@ -2924,10 +2922,10 @@
         <v>199607</v>
       </c>
       <c r="B260" s="1">
-        <v>-0.28658702969551086</v>
+        <v>-0.28658702969551087</v>
       </c>
       <c r="C260" s="1">
-        <v>0.088358849287033081</v>
+        <v>0.1034202054142952</v>
       </c>
     </row>
     <row r="261">
@@ -2935,10 +2933,10 @@
         <v>199608</v>
       </c>
       <c r="B261" s="1">
-        <v>0.088021062314510345</v>
+        <v>0.088021062314510346</v>
       </c>
       <c r="C261" s="1">
-        <v>0.2340257316827774</v>
+        <v>0.049949288368225098</v>
       </c>
     </row>
     <row r="262">
@@ -2949,7 +2947,7 @@
         <v>0.045286640524864197</v>
       </c>
       <c r="C262" s="1">
-        <v>-0.13845217227935791</v>
+        <v>-0.15373711287975311</v>
       </c>
     </row>
     <row r="263">
@@ -2960,7 +2958,7 @@
         <v>0.053469829261302948</v>
       </c>
       <c r="C263" s="1">
-        <v>-0.051180202513933182</v>
+        <v>-0.080571681261062622</v>
       </c>
     </row>
     <row r="264">
@@ -2971,7 +2969,7 @@
         <v>0.32942509651184082</v>
       </c>
       <c r="C264" s="1">
-        <v>0.024932608008384705</v>
+        <v>0.15260839462280273</v>
       </c>
     </row>
     <row r="265">
@@ -2982,7 +2980,7 @@
         <v>0.1812184751033783</v>
       </c>
       <c r="C265" s="1">
-        <v>-0.024267513304948807</v>
+        <v>-0.19562692940235138</v>
       </c>
     </row>
     <row r="266">
@@ -2993,7 +2991,7 @@
         <v>0.33669903874397278</v>
       </c>
       <c r="C266" s="1">
-        <v>-0.12425757944583893</v>
+        <v>-0.20413535833358765</v>
       </c>
     </row>
     <row r="267">
@@ -3004,7 +3002,7 @@
         <v>-0.094282157719135284</v>
       </c>
       <c r="C267" s="1">
-        <v>-0.35283014178276062</v>
+        <v>-0.35546296834945679</v>
       </c>
     </row>
     <row r="268">
@@ -3015,7 +3013,7 @@
         <v>-0.022451957687735558</v>
       </c>
       <c r="C268" s="1">
-        <v>-0.29090243577957153</v>
+        <v>-0.22767525911331177</v>
       </c>
     </row>
     <row r="269">
@@ -3026,7 +3024,7 @@
         <v>0.057561416178941727</v>
       </c>
       <c r="C269" s="1">
-        <v>-0.12858732044696808</v>
+        <v>-0.28396299481391907</v>
       </c>
     </row>
     <row r="270">
@@ -3037,7 +3035,7 @@
         <v>0.18849240243434906</v>
       </c>
       <c r="C270" s="1">
-        <v>-0.22936862707138062</v>
+        <v>-0.16318728029727936</v>
       </c>
     </row>
     <row r="271">
@@ -3048,7 +3046,7 @@
         <v>0.17348991334438324</v>
       </c>
       <c r="C271" s="1">
-        <v>-0.2940983772277832</v>
+        <v>-0.26660293340682983</v>
       </c>
     </row>
     <row r="272">
@@ -3059,7 +3057,7 @@
         <v>0.2325906902551651</v>
       </c>
       <c r="C272" s="1">
-        <v>-0.46483507752418518</v>
+        <v>-0.3134937584400177</v>
       </c>
     </row>
     <row r="273">
@@ -3070,7 +3068,7 @@
         <v>-0.11292163282632828</v>
       </c>
       <c r="C273" s="1">
-        <v>-0.23592537641525269</v>
+        <v>-0.11041674762964249</v>
       </c>
     </row>
     <row r="274">
@@ -3081,7 +3079,7 @@
         <v>0.14984957873821259</v>
       </c>
       <c r="C274" s="1">
-        <v>0.26868227124214172</v>
+        <v>0.20647487044334412</v>
       </c>
     </row>
     <row r="275">
@@ -3092,7 +3090,7 @@
         <v>-0.22203078866004944</v>
       </c>
       <c r="C275" s="1">
-        <v>0.20203396677970886</v>
+        <v>0.25636816024780273</v>
       </c>
     </row>
     <row r="276">
@@ -3103,7 +3101,7 @@
         <v>-0.25612741708755493</v>
       </c>
       <c r="C276" s="1">
-        <v>0.0090171154588460922</v>
+        <v>0.060130711644887924</v>
       </c>
     </row>
     <row r="277">
@@ -3114,7 +3112,7 @@
         <v>0.036194209009408951</v>
       </c>
       <c r="C277" s="1">
-        <v>-0.096028365194797516</v>
+        <v>-0.2647683322429657</v>
       </c>
     </row>
     <row r="278">
@@ -3125,7 +3123,7 @@
         <v>-0.25158116221427917</v>
       </c>
       <c r="C278" s="1">
-        <v>-0.35323968529701233</v>
+        <v>-0.3528980016708374</v>
       </c>
     </row>
     <row r="279">
@@ -3136,7 +3134,7 @@
         <v>0.12302691489458084</v>
       </c>
       <c r="C279" s="1">
-        <v>-0.14554271101951599</v>
+        <v>-0.1593676507472992</v>
       </c>
     </row>
     <row r="280">
@@ -3147,7 +3145,7 @@
         <v>0.38261580467224121</v>
       </c>
       <c r="C280" s="1">
-        <v>-0.17878471314907074</v>
+        <v>-0.2178492546081543</v>
       </c>
     </row>
     <row r="281">
@@ -3158,7 +3156,7 @@
         <v>0.089384928345680237</v>
       </c>
       <c r="C281" s="1">
-        <v>0.2377496212720871</v>
+        <v>0.054493308067321777</v>
       </c>
     </row>
     <row r="282">
@@ -3169,7 +3167,7 @@
         <v>-0.39524158835411072</v>
       </c>
       <c r="C282" s="1">
-        <v>0.16597218811511993</v>
+        <v>0.26958093047142029</v>
       </c>
     </row>
     <row r="283">
@@ -3180,7 +3178,7 @@
         <v>-0.12246868759393692</v>
       </c>
       <c r="C283" s="1">
-        <v>-0.30187720060348511</v>
+        <v>-0.24916109442710877</v>
       </c>
     </row>
     <row r="284">
@@ -3191,7 +3189,7 @@
         <v>-0.05927630141377449</v>
       </c>
       <c r="C284" s="1">
-        <v>0.18390084803104401</v>
+        <v>-0.01076037809252739</v>
       </c>
     </row>
     <row r="285">
@@ -3202,7 +3200,7 @@
         <v>-1.1994670629501343</v>
       </c>
       <c r="C285" s="1">
-        <v>0.11992532759904861</v>
+        <v>0.25547674298286438</v>
       </c>
     </row>
     <row r="286">
@@ -3213,7 +3211,7 @@
         <v>-0.40024241805076599</v>
       </c>
       <c r="C286" s="1">
-        <v>-0.043192926794290543</v>
+        <v>-0.1234746128320694</v>
       </c>
     </row>
     <row r="287">
@@ -3224,7 +3222,7 @@
         <v>0.61856436729431152</v>
       </c>
       <c r="C287" s="1">
-        <v>0.33132642507553101</v>
+        <v>0.12232118099927902</v>
       </c>
     </row>
     <row r="288">
@@ -3235,7 +3233,7 @@
         <v>-0.35478028655052185</v>
       </c>
       <c r="C288" s="1">
-        <v>-0.028085146099328995</v>
+        <v>0.035351164638996124</v>
       </c>
     </row>
     <row r="289">
@@ -3246,7 +3244,7 @@
         <v>-0.22885012626647949</v>
       </c>
       <c r="C289" s="1">
-        <v>-0.23835279047489166</v>
+        <v>-0.17344501614570618</v>
       </c>
     </row>
     <row r="290">
@@ -3257,7 +3255,7 @@
         <v>0.42216786742210388</v>
       </c>
       <c r="C290" s="1">
-        <v>-0.039648249745368958</v>
+        <v>-0.040199104696512222</v>
       </c>
     </row>
     <row r="291">
@@ -3268,7 +3266,7 @@
         <v>-0.25158116221427917</v>
       </c>
       <c r="C291" s="1">
-        <v>-0.38570544123649597</v>
+        <v>-0.30717352032661438</v>
       </c>
     </row>
     <row r="292">
@@ -3279,7 +3277,7 @@
         <v>0.29805618524551392</v>
       </c>
       <c r="C292" s="1">
-        <v>-0.20876045525074005</v>
+        <v>-0.27881622314453125</v>
       </c>
     </row>
     <row r="293">
@@ -3290,7 +3288,7 @@
         <v>0.32533350586891174</v>
       </c>
       <c r="C293" s="1">
-        <v>-0.029355702921748161</v>
+        <v>-0.016657914966344833</v>
       </c>
     </row>
     <row r="294">
@@ -3301,7 +3299,7 @@
         <v>-0.1092846617102623</v>
       </c>
       <c r="C294" s="1">
-        <v>-0.08962046355009079</v>
+        <v>0.050188634544610977</v>
       </c>
     </row>
     <row r="295">
@@ -3312,7 +3310,7 @@
         <v>-0.12292331457138062</v>
       </c>
       <c r="C295" s="1">
-        <v>-0.22721852362155914</v>
+        <v>-0.1573840081691742</v>
       </c>
     </row>
     <row r="296">
@@ -3323,7 +3321,7 @@
         <v>0.083474844694137573</v>
       </c>
       <c r="C296" s="1">
-        <v>-0.1568761020898819</v>
+        <v>0.013781927525997162</v>
       </c>
     </row>
     <row r="297">
@@ -3334,7 +3332,7 @@
         <v>0.11711683869361877</v>
       </c>
       <c r="C297" s="1">
-        <v>0.045567166060209274</v>
+        <v>0.23908761143684387</v>
       </c>
     </row>
     <row r="298">
@@ -3345,7 +3343,7 @@
         <v>-0.053366221487522125</v>
       </c>
       <c r="C298" s="1">
-        <v>-0.08130887895822525</v>
+        <v>-0.22183513641357422</v>
       </c>
     </row>
     <row r="299">
@@ -3356,7 +3354,7 @@
         <v>-0.20839214324951172</v>
       </c>
       <c r="C299" s="1">
-        <v>0.090654581785202026</v>
+        <v>0.074545226991176605</v>
       </c>
     </row>
     <row r="300">
@@ -3367,7 +3365,7 @@
         <v>0.26441419124603271</v>
       </c>
       <c r="C300" s="1">
-        <v>-0.43071159720420837</v>
+        <v>-0.40691912174224854</v>
       </c>
     </row>
     <row r="301">
@@ -3378,7 +3376,7 @@
         <v>0.43626111745834351</v>
       </c>
       <c r="C301" s="1">
-        <v>-0.25553783774375916</v>
+        <v>-0.18589988350868225</v>
       </c>
     </row>
     <row r="302">
@@ -3389,7 +3387,7 @@
         <v>-0.26249212026596069</v>
       </c>
       <c r="C302" s="1">
-        <v>-0.034299924969673157</v>
+        <v>-0.074745625257492066</v>
       </c>
     </row>
     <row r="303">
@@ -3400,7 +3398,7 @@
         <v>0.046195883303880692</v>
       </c>
       <c r="C303" s="1">
-        <v>-0.39111042022705078</v>
+        <v>-0.37409242987632751</v>
       </c>
     </row>
     <row r="304">
@@ -3411,7 +3409,7 @@
         <v>0.026647165417671204</v>
       </c>
       <c r="C304" s="1">
-        <v>-0.3149859607219696</v>
+        <v>-0.2387700080871582</v>
       </c>
     </row>
     <row r="305">
@@ -3422,7 +3420,7 @@
         <v>-0.13201573491096497</v>
       </c>
       <c r="C305" s="1">
-        <v>-0.20841658115386963</v>
+        <v>-0.18999990820884705</v>
       </c>
     </row>
     <row r="306">
@@ -3433,7 +3431,7 @@
         <v>0.13439244031906128</v>
       </c>
       <c r="C306" s="1">
-        <v>-0.72079980373382568</v>
+        <v>-0.61116939783096313</v>
       </c>
     </row>
     <row r="307">
@@ -3441,10 +3439,10 @@
         <v>200006</v>
       </c>
       <c r="B307" s="1">
-        <v>0.17712686955928802</v>
+        <v>0.17712686955928803</v>
       </c>
       <c r="C307" s="1">
-        <v>0.36647602915763855</v>
+        <v>0.29697641730308533</v>
       </c>
     </row>
     <row r="308">
@@ -3455,7 +3453,7 @@
         <v>0.035284966230392456</v>
       </c>
       <c r="C308" s="1">
-        <v>-0.18443743884563446</v>
+        <v>0.02615685760974884</v>
       </c>
     </row>
     <row r="309">
@@ -3466,7 +3464,7 @@
         <v>0.36079397797584534</v>
       </c>
       <c r="C309" s="1">
-        <v>-0.074652530252933502</v>
+        <v>-0.25627541542053223</v>
       </c>
     </row>
     <row r="310">
@@ -3477,7 +3475,7 @@
         <v>-0.15247370302677155</v>
       </c>
       <c r="C310" s="1">
-        <v>-0.34881380200386047</v>
+        <v>-0.4644719660282135</v>
       </c>
     </row>
     <row r="311">
@@ -3488,7 +3486,7 @@
         <v>-0.070641838014125824</v>
       </c>
       <c r="C311" s="1">
-        <v>0.011690139770507812</v>
+        <v>-0.15885744988918304</v>
       </c>
     </row>
     <row r="312">
@@ -3499,7 +3497,7 @@
         <v>-0.22521314024925232</v>
       </c>
       <c r="C312" s="1">
-        <v>0.046832051128149033</v>
+        <v>5.4694381105946377e-05</v>
       </c>
     </row>
     <row r="313">
@@ -3510,7 +3508,7 @@
         <v>0.013008514419198036</v>
       </c>
       <c r="C313" s="1">
-        <v>0.25744864344596863</v>
+        <v>0.36832669377326965</v>
       </c>
     </row>
     <row r="314">
@@ -3521,7 +3519,7 @@
         <v>0.13302859663963318</v>
       </c>
       <c r="C314" s="1">
-        <v>0.21387968957424164</v>
+        <v>0.089241631329059601</v>
       </c>
     </row>
     <row r="315">
@@ -3532,7 +3530,7 @@
         <v>-0.12155944854021072</v>
       </c>
       <c r="C315" s="1">
-        <v>-0.13157081604003906</v>
+        <v>-0.23868681490421295</v>
       </c>
     </row>
     <row r="316">
@@ -3543,7 +3541,7 @@
         <v>-0.34068700671195984</v>
       </c>
       <c r="C316" s="1">
-        <v>-0.14762933552265167</v>
+        <v>-0.10538376122713089</v>
       </c>
     </row>
     <row r="317">
@@ -3554,7 +3552,7 @@
         <v>0.28805452585220337</v>
       </c>
       <c r="C317" s="1">
-        <v>-0.24988694489002228</v>
+        <v>-0.242169588804245</v>
       </c>
     </row>
     <row r="318">
@@ -3565,7 +3563,7 @@
         <v>-0.039727576076984406</v>
       </c>
       <c r="C318" s="1">
-        <v>-0.043193362653255463</v>
+        <v>-0.094014570116996765</v>
       </c>
     </row>
     <row r="319">
@@ -3573,10 +3571,10 @@
         <v>200106</v>
       </c>
       <c r="B319" s="1">
-        <v>-0.22066693007946014</v>
+        <v>-0.22066693007946015</v>
       </c>
       <c r="C319" s="1">
-        <v>0.007829153910279274</v>
+        <v>-0.14901314675807953</v>
       </c>
     </row>
     <row r="320">
@@ -3587,7 +3585,7 @@
         <v>-0.14065355062484741</v>
       </c>
       <c r="C320" s="1">
-        <v>-0.018212443217635155</v>
+        <v>0.38822406530380249</v>
       </c>
     </row>
     <row r="321">
@@ -3598,7 +3596,7 @@
         <v>-0.32022902369499207</v>
       </c>
       <c r="C321" s="1">
-        <v>0.28418028354644775</v>
+        <v>0.39693185687065125</v>
       </c>
     </row>
     <row r="322">
@@ -3609,7 +3607,7 @@
         <v>-0.67801612615585327</v>
       </c>
       <c r="C322" s="1">
-        <v>0.14689157903194427</v>
+        <v>0.126659095287323</v>
       </c>
     </row>
     <row r="323">
@@ -3620,7 +3618,7 @@
         <v>0.023919433355331421</v>
       </c>
       <c r="C323" s="1">
-        <v>0.19462370872497559</v>
+        <v>-0.00044712869566865265</v>
       </c>
     </row>
     <row r="324">
@@ -3631,7 +3629,7 @@
         <v>0.24895705282688141</v>
       </c>
       <c r="C324" s="1">
-        <v>0.041713885962963104</v>
+        <v>-0.13664056360721588</v>
       </c>
     </row>
     <row r="325">
@@ -3642,7 +3640,7 @@
         <v>0.20213106274604797</v>
       </c>
       <c r="C325" s="1">
-        <v>-0.23589374125003815</v>
+        <v>-0.18410708010196686</v>
       </c>
     </row>
     <row r="326">
@@ -3653,7 +3651,7 @@
         <v>-0.1765686422586441</v>
       </c>
       <c r="C326" s="1">
-        <v>-0.064496785402297974</v>
+        <v>0.0010796537389978766</v>
       </c>
     </row>
     <row r="327">
@@ -3664,7 +3662,7 @@
         <v>0.10211432725191116</v>
       </c>
       <c r="C327" s="1">
-        <v>-0.10958527773618698</v>
+        <v>-0.035946667194366455</v>
       </c>
     </row>
     <row r="328">
@@ -3675,7 +3673,7 @@
         <v>0.31033098697662354</v>
       </c>
       <c r="C328" s="1">
-        <v>0.23487867414951324</v>
+        <v>0.17513701319694519</v>
       </c>
     </row>
     <row r="329">
@@ -3686,7 +3684,7 @@
         <v>-0.20839214324951172</v>
       </c>
       <c r="C329" s="1">
-        <v>-0.090156994760036469</v>
+        <v>0.024895073845982552</v>
       </c>
     </row>
     <row r="330">
@@ -3697,7 +3695,7 @@
         <v>-0.2106652557849884</v>
       </c>
       <c r="C330" s="1">
-        <v>0.46564418077468872</v>
+        <v>0.45932388305664063</v>
       </c>
     </row>
     <row r="331">
@@ -3708,7 +3706,7 @@
         <v>-0.40569788217544556</v>
       </c>
       <c r="C331" s="1">
-        <v>0.79842478036880493</v>
+        <v>0.58123260736465454</v>
       </c>
     </row>
     <row r="332">
@@ -3719,7 +3717,7 @@
         <v>-0.39069536328315735</v>
       </c>
       <c r="C332" s="1">
-        <v>0.39333751797676086</v>
+        <v>0.48447778820991516</v>
       </c>
     </row>
     <row r="333">
@@ -3730,7 +3728,7 @@
         <v>-0.093827530741691589</v>
       </c>
       <c r="C333" s="1">
-        <v>-0.22645756602287292</v>
+        <v>-0.026607690379023552</v>
       </c>
     </row>
     <row r="334">
@@ -3741,7 +3739,7 @@
         <v>-0.66255903244018555</v>
       </c>
       <c r="C334" s="1">
-        <v>0.23707783222198486</v>
+        <v>0.15095457434654236</v>
       </c>
     </row>
     <row r="335">
@@ -3752,7 +3750,7 @@
         <v>0.15121343731880188</v>
       </c>
       <c r="C335" s="1">
-        <v>-0.14924709498882294</v>
+        <v>-0.13033600151538849</v>
       </c>
     </row>
     <row r="336">
@@ -3763,7 +3761,7 @@
         <v>0.17939998209476471</v>
       </c>
       <c r="C336" s="1">
-        <v>0.13756832480430603</v>
+        <v>0.12179384380578995</v>
       </c>
     </row>
     <row r="337">
@@ -3771,10 +3769,10 @@
         <v>200212</v>
       </c>
       <c r="B337" s="1">
-        <v>-0.17293167114257812</v>
+        <v>-0.17293167114257813</v>
       </c>
       <c r="C337" s="1">
-        <v>0.15594197809696198</v>
+        <v>0.051144294440746307</v>
       </c>
     </row>
     <row r="338">
@@ -3785,7 +3783,7 @@
         <v>-0.29340636730194092</v>
       </c>
       <c r="C338" s="1">
-        <v>0.19115585088729858</v>
+        <v>-0.27345988154411316</v>
       </c>
     </row>
     <row r="339">
@@ -3796,7 +3794,7 @@
         <v>-0.25021731853485107</v>
       </c>
       <c r="C339" s="1">
-        <v>-0.15766571462154388</v>
+        <v>-0.087654165923595429</v>
       </c>
     </row>
     <row r="340">
@@ -3807,7 +3805,7 @@
         <v>0.033011864870786667</v>
       </c>
       <c r="C340" s="1">
-        <v>-0.46811002492904663</v>
+        <v>-0.17199143767356873</v>
       </c>
     </row>
     <row r="341">
@@ -3818,7 +3816,7 @@
         <v>0.3517015278339386</v>
       </c>
       <c r="C341" s="1">
-        <v>0.0018062996678054333</v>
+        <v>0.26258111000061035</v>
       </c>
     </row>
     <row r="342">
@@ -3829,7 +3827,7 @@
         <v>0.17485375702381134</v>
       </c>
       <c r="C342" s="1">
-        <v>0.45748460292816162</v>
+        <v>0.67036032676696777</v>
       </c>
     </row>
     <row r="343">
@@ -3840,7 +3838,7 @@
         <v>0.27623435854911804</v>
       </c>
       <c r="C343" s="1">
-        <v>-0.38923341035842896</v>
+        <v>-0.21879243850708008</v>
       </c>
     </row>
     <row r="344">
@@ -3851,7 +3849,7 @@
         <v>0.25714027881622314</v>
       </c>
       <c r="C344" s="1">
-        <v>-0.55446213483810425</v>
+        <v>-0.33979618549346924</v>
       </c>
     </row>
     <row r="345">
@@ -3862,7 +3860,7 @@
         <v>0.14575798809528351</v>
       </c>
       <c r="C345" s="1">
-        <v>-0.24952316284179688</v>
+        <v>-0.2119007408618927</v>
       </c>
     </row>
     <row r="346">
@@ -3873,7 +3871,7 @@
         <v>-0.32568448781967163</v>
       </c>
       <c r="C346" s="1">
-        <v>0.096387788653373718</v>
+        <v>0.067113302648067474</v>
       </c>
     </row>
     <row r="347">
@@ -3884,7 +3882,7 @@
         <v>0.50354510545730591</v>
       </c>
       <c r="C347" s="1">
-        <v>0.44470435380935669</v>
+        <v>0.24565672874450684</v>
       </c>
     </row>
     <row r="348">
@@ -3892,10 +3890,10 @@
         <v>200311</v>
       </c>
       <c r="B348" s="1">
-        <v>0.024828674271702766</v>
+        <v>0.024828674271702767</v>
       </c>
       <c r="C348" s="1">
-        <v>-0.010914605110883713</v>
+        <v>0.043265718966722489</v>
       </c>
     </row>
     <row r="349">
@@ -3906,7 +3904,7 @@
         <v>0.25304868817329407</v>
       </c>
       <c r="C349" s="1">
-        <v>0.58045488595962524</v>
+        <v>0.37451905012130737</v>
       </c>
     </row>
     <row r="350">
@@ -3917,7 +3915,7 @@
         <v>0.24122849106788635</v>
       </c>
       <c r="C350" s="1">
-        <v>-0.2302289754152298</v>
+        <v>-0.10938963294029236</v>
       </c>
     </row>
     <row r="351">
@@ -3928,7 +3926,7 @@
         <v>0.3698863685131073</v>
       </c>
       <c r="C351" s="1">
-        <v>-0.298993319272995</v>
+        <v>-0.23046201467514038</v>
       </c>
     </row>
     <row r="352">
@@ -3939,7 +3937,7 @@
         <v>-0.16656696796417236</v>
       </c>
       <c r="C352" s="1">
-        <v>-0.13658192753791809</v>
+        <v>-0.15508808195590973</v>
       </c>
     </row>
     <row r="353">
@@ -3950,7 +3948,7 @@
         <v>-0.17247705161571503</v>
       </c>
       <c r="C353" s="1">
-        <v>0.051355853676795959</v>
+        <v>0.10464491695165634</v>
       </c>
     </row>
     <row r="354">
@@ -3958,10 +3956,10 @@
         <v>200405</v>
       </c>
       <c r="B354" s="1">
-        <v>0.024828674271702766</v>
+        <v>0.024828674271702767</v>
       </c>
       <c r="C354" s="1">
-        <v>0.029040232300758362</v>
+        <v>0.089772835373878479</v>
       </c>
     </row>
     <row r="355">
@@ -3972,7 +3970,7 @@
         <v>0.23759151995182037</v>
       </c>
       <c r="C355" s="1">
-        <v>0.066197745501995087</v>
+        <v>-0.091083548963069916</v>
       </c>
     </row>
     <row r="356">
@@ -3983,7 +3981,7 @@
         <v>-0.072460323572158813</v>
       </c>
       <c r="C356" s="1">
-        <v>-0.033374100923538208</v>
+        <v>0.058183163404464722</v>
       </c>
     </row>
     <row r="357">
@@ -3994,7 +3992,7 @@
         <v>0.011644652113318443</v>
       </c>
       <c r="C357" s="1">
-        <v>0.2091643363237381</v>
+        <v>0.31661719083786011</v>
       </c>
     </row>
     <row r="358">
@@ -4005,7 +4003,7 @@
         <v>0.33760824799537659</v>
       </c>
       <c r="C358" s="1">
-        <v>-0.31150582432746887</v>
+        <v>-0.32772764563560486</v>
       </c>
     </row>
     <row r="359">
@@ -4013,10 +4011,10 @@
         <v>200410</v>
       </c>
       <c r="B359" s="1">
-        <v>-0.17293167114257812</v>
+        <v>-0.17293167114257813</v>
       </c>
       <c r="C359" s="1">
-        <v>0.22259372472763062</v>
+        <v>0.25806936621665955</v>
       </c>
     </row>
     <row r="360">
@@ -4027,7 +4025,7 @@
         <v>0.30669400095939636</v>
       </c>
       <c r="C360" s="1">
-        <v>0.70103555917739868</v>
+        <v>0.47333413362503052</v>
       </c>
     </row>
     <row r="361">
@@ -4038,7 +4036,7 @@
         <v>-0.088826701045036316</v>
       </c>
       <c r="C361" s="1">
-        <v>0.21437422931194305</v>
+        <v>0.31111878156661987</v>
       </c>
     </row>
     <row r="362">
@@ -4049,7 +4047,7 @@
         <v>0.070745453238487244</v>
       </c>
       <c r="C362" s="1">
-        <v>-0.24170872569084167</v>
+        <v>-0.084155865013599396</v>
       </c>
     </row>
     <row r="363">
@@ -4060,7 +4058,7 @@
         <v>0.40943843126296997</v>
       </c>
       <c r="C363" s="1">
-        <v>-0.3912232518196106</v>
+        <v>-0.30806389451026917</v>
       </c>
     </row>
     <row r="364">
@@ -4071,7 +4069,7 @@
         <v>-0.11383087933063507</v>
       </c>
       <c r="C364" s="1">
-        <v>0.24209055304527283</v>
+        <v>0.19675931334495545</v>
       </c>
     </row>
     <row r="365">
@@ -4082,7 +4080,7 @@
         <v>-0.22657701373100281</v>
       </c>
       <c r="C365" s="1">
-        <v>-0.37281954288482666</v>
+        <v>-0.35157197713851929</v>
       </c>
     </row>
     <row r="366">
@@ -4093,7 +4091,7 @@
         <v>0.10620592534542084</v>
       </c>
       <c r="C366" s="1">
-        <v>-0.11684191972017288</v>
+        <v>-0.11917922645807266</v>
       </c>
     </row>
     <row r="367">
@@ -4104,7 +4102,7 @@
         <v>0.49763500690460205</v>
       </c>
       <c r="C367" s="1">
-        <v>0.042400162667036057</v>
+        <v>-0.16034512221813202</v>
       </c>
     </row>
     <row r="368">
@@ -4115,7 +4113,7 @@
         <v>0.21258735656738281</v>
       </c>
       <c r="C368" s="1">
-        <v>-0.23271283507347107</v>
+        <v>-0.073627054691314697</v>
       </c>
     </row>
     <row r="369">
@@ -4126,7 +4124,7 @@
         <v>0.25032094120979309</v>
       </c>
       <c r="C369" s="1">
-        <v>0.0059381518512964249</v>
+        <v>0.077796407043933868</v>
       </c>
     </row>
     <row r="370">
@@ -4137,7 +4135,7 @@
         <v>0.15303191542625427</v>
       </c>
       <c r="C370" s="1">
-        <v>-0.041482370346784592</v>
+        <v>-0.12427856028079987</v>
       </c>
     </row>
     <row r="371">
@@ -4148,7 +4146,7 @@
         <v>-0.40433400869369507</v>
       </c>
       <c r="C371" s="1">
-        <v>-0.17188198864459991</v>
+        <v>-0.11110556870698929</v>
       </c>
     </row>
     <row r="372">
@@ -4159,7 +4157,7 @@
         <v>0.10984288901090622</v>
       </c>
       <c r="C372" s="1">
-        <v>-0.011722167022526264</v>
+        <v>-0.18598733842372894</v>
       </c>
     </row>
     <row r="373">
@@ -4170,7 +4168,7 @@
         <v>0.16576133668422699</v>
       </c>
       <c r="C373" s="1">
-        <v>-0.22454439103603363</v>
+        <v>-0.099193796515464783</v>
       </c>
     </row>
     <row r="374">
@@ -4181,7 +4179,7 @@
         <v>0.42716866731643677</v>
       </c>
       <c r="C374" s="1">
-        <v>-0.022834127768874168</v>
+        <v>0.12474196404218674</v>
       </c>
     </row>
     <row r="375">
@@ -4192,7 +4190,7 @@
         <v>-0.022451957687735558</v>
       </c>
       <c r="C375" s="1">
-        <v>-0.24437519907951355</v>
+        <v>-0.34908398985862732</v>
       </c>
     </row>
     <row r="376">
@@ -4203,7 +4201,7 @@
         <v>0.33897215127944946</v>
       </c>
       <c r="C376" s="1">
-        <v>0.038972247391939163</v>
+        <v>0.059896502643823624</v>
       </c>
     </row>
     <row r="377">
@@ -4214,7 +4212,7 @@
         <v>0.10029583424329758</v>
       </c>
       <c r="C377" s="1">
-        <v>0.29629933834075928</v>
+        <v>0.15971177816390991</v>
       </c>
     </row>
     <row r="378">
@@ -4225,7 +4223,7 @@
         <v>-0.4488869309425354</v>
       </c>
       <c r="C378" s="1">
-        <v>0.6786695122718811</v>
+        <v>0.47425350546836853</v>
       </c>
     </row>
     <row r="379">
@@ -4236,7 +4234,7 @@
         <v>-0.077915780246257782</v>
       </c>
       <c r="C379" s="1">
-        <v>-0.24239824712276459</v>
+        <v>-0.10588440299034119</v>
       </c>
     </row>
     <row r="380">
@@ -4247,7 +4245,7 @@
         <v>0.081201747059822083</v>
       </c>
       <c r="C380" s="1">
-        <v>-0.15916192531585693</v>
+        <v>0.011959647759795189</v>
       </c>
     </row>
     <row r="381">
@@ -4258,7 +4256,7 @@
         <v>-0.11292163282632828</v>
       </c>
       <c r="C381" s="1">
-        <v>0.25230032205581665</v>
+        <v>0.067196637392044067</v>
       </c>
     </row>
     <row r="382">
@@ -4269,7 +4267,7 @@
         <v>-0.25567278265953064</v>
       </c>
       <c r="C382" s="1">
-        <v>-0.43505275249481201</v>
+        <v>-0.67403727769851685</v>
       </c>
     </row>
     <row r="383">
@@ -4280,7 +4278,7 @@
         <v>0.35943010449409485</v>
       </c>
       <c r="C383" s="1">
-        <v>-0.35902103781700134</v>
+        <v>-0.29885438084602356</v>
       </c>
     </row>
     <row r="384">
@@ -4291,7 +4289,7 @@
         <v>0.06892695277929306</v>
       </c>
       <c r="C384" s="1">
-        <v>0.32556632161140442</v>
+        <v>0.42773506045341492</v>
       </c>
     </row>
     <row r="385">
@@ -4302,7 +4300,7 @@
         <v>0.25304868817329407</v>
       </c>
       <c r="C385" s="1">
-        <v>0.13655760884284973</v>
+        <v>0.34350904822349548</v>
       </c>
     </row>
     <row r="386">
@@ -4310,10 +4308,10 @@
         <v>200701</v>
       </c>
       <c r="B386" s="1">
-        <v>0.13848406076431274</v>
+        <v>0.13848406076431275</v>
       </c>
       <c r="C386" s="1">
-        <v>-0.3756067156791687</v>
+        <v>0.023853002116084099</v>
       </c>
     </row>
     <row r="387">
@@ -4324,7 +4322,7 @@
         <v>-0.28567779064178467</v>
       </c>
       <c r="C387" s="1">
-        <v>0.25046983361244202</v>
+        <v>0.23543624579906464</v>
       </c>
     </row>
     <row r="388">
@@ -4335,7 +4333,7 @@
         <v>0.13621093332767487</v>
       </c>
       <c r="C388" s="1">
-        <v>-0.0042096995748579502</v>
+        <v>-0.065269917249679565</v>
       </c>
     </row>
     <row r="389">
@@ -4346,7 +4344,7 @@
         <v>0.094840385019779205</v>
       </c>
       <c r="C389" s="1">
-        <v>0.25543487071990967</v>
+        <v>0.086029626429080963</v>
       </c>
     </row>
     <row r="390">
@@ -4357,7 +4355,7 @@
         <v>0.11438909918069839</v>
       </c>
       <c r="C390" s="1">
-        <v>0.0076603922061622143</v>
+        <v>0.041987620294094086</v>
       </c>
     </row>
     <row r="391">
@@ -4368,7 +4366,7 @@
         <v>0.15212267637252808</v>
       </c>
       <c r="C391" s="1">
-        <v>0.014270013198256493</v>
+        <v>0.11427275836467743</v>
       </c>
     </row>
     <row r="392">
@@ -4379,7 +4377,7 @@
         <v>-0.17929635941982269</v>
       </c>
       <c r="C392" s="1">
-        <v>0.19739985466003418</v>
+        <v>0.36855483055114746</v>
       </c>
     </row>
     <row r="393">
@@ -4390,7 +4388,7 @@
         <v>-0.2293047308921814</v>
       </c>
       <c r="C393" s="1">
-        <v>-0.1605750173330307</v>
+        <v>-0.036124479025602341</v>
       </c>
     </row>
     <row r="394">
@@ -4401,7 +4399,7 @@
         <v>0.22440749406814575</v>
       </c>
       <c r="C394" s="1">
-        <v>0.22260047495365143</v>
+        <v>0.12199462950229645</v>
       </c>
     </row>
     <row r="395">
@@ -4412,7 +4410,7 @@
         <v>0.12620927393436432</v>
       </c>
       <c r="C395" s="1">
-        <v>0.33548107743263245</v>
+        <v>0.35465648770332337</v>
       </c>
     </row>
     <row r="396">
@@ -4423,7 +4421,7 @@
         <v>-0.19157114624977112</v>
       </c>
       <c r="C396" s="1">
-        <v>-0.031639542430639267</v>
+        <v>-0.34869959950447083</v>
       </c>
     </row>
     <row r="397">
@@ -4434,7 +4432,7 @@
         <v>-0.067914105951786041</v>
       </c>
       <c r="C397" s="1">
-        <v>-0.18657581508159637</v>
+        <v>-0.29084178805351257</v>
       </c>
     </row>
     <row r="398">
@@ -4445,7 +4443,7 @@
         <v>-0.91487395763397217</v>
       </c>
       <c r="C398" s="1">
-        <v>0.17729569971561432</v>
+        <v>0.39211621880531311</v>
       </c>
     </row>
     <row r="399">
@@ -4456,7 +4454,7 @@
         <v>0.29714691638946533</v>
       </c>
       <c r="C399" s="1">
-        <v>-0.067938290536403656</v>
+        <v>-0.1296519935131073</v>
       </c>
     </row>
     <row r="400">
@@ -4464,10 +4462,10 @@
         <v>200803</v>
       </c>
       <c r="B400" s="1">
-        <v>-0.20611903071403503</v>
+        <v>-0.20611903071403504</v>
       </c>
       <c r="C400" s="1">
-        <v>0.63330698013305664</v>
+        <v>0.43142855167388916</v>
       </c>
     </row>
     <row r="401">
@@ -4478,7 +4476,7 @@
         <v>0.48990646004676819</v>
       </c>
       <c r="C401" s="1">
-        <v>0.29950356483459473</v>
+        <v>0.1069239154458046</v>
       </c>
     </row>
     <row r="402">
@@ -4489,7 +4487,7 @@
         <v>0.26941505074501038</v>
       </c>
       <c r="C402" s="1">
-        <v>0.15324461460113525</v>
+        <v>-0.028890214860439301</v>
       </c>
     </row>
     <row r="403">
@@ -4500,7 +4498,7 @@
         <v>-0.32522988319396973</v>
       </c>
       <c r="C403" s="1">
-        <v>-0.16089160740375519</v>
+        <v>-0.1104169636964798</v>
       </c>
     </row>
     <row r="404">
@@ -4508,10 +4506,10 @@
         <v>200807</v>
       </c>
       <c r="B404" s="1">
-        <v>-0.39615082740783691</v>
+        <v>-0.39615082740783692</v>
       </c>
       <c r="C404" s="1">
-        <v>0.013706394471228123</v>
+        <v>-0.028166793286800385</v>
       </c>
     </row>
     <row r="405">
@@ -4522,7 +4520,7 @@
         <v>-0.071096457540988922</v>
       </c>
       <c r="C405" s="1">
-        <v>-0.36881420016288757</v>
+        <v>-0.31536710262298584</v>
       </c>
     </row>
     <row r="406">
@@ -4533,7 +4531,7 @@
         <v>-1.0885393619537354</v>
       </c>
       <c r="C406" s="1">
-        <v>-0.63659179210662842</v>
+        <v>-0.83773642778396607</v>
       </c>
     </row>
     <row r="407">
@@ -4544,7 +4542,7 @@
         <v>-0.99215954542160034</v>
       </c>
       <c r="C407" s="1">
-        <v>-1.3874127864837646</v>
+        <v>-1.282532811164856</v>
       </c>
     </row>
     <row r="408">
@@ -4555,7 +4553,7 @@
         <v>-0.48161965608596802</v>
       </c>
       <c r="C408" s="1">
-        <v>-0.69078147411346436</v>
+        <v>-0.42538857460021973</v>
       </c>
     </row>
     <row r="409">
@@ -4566,7 +4564,7 @@
         <v>-0.0092679383233189583</v>
       </c>
       <c r="C409" s="1">
-        <v>-0.17614877223968506</v>
+        <v>-0.040000103414058685</v>
       </c>
     </row>
     <row r="410">
@@ -4577,7 +4575,7 @@
         <v>0.033011864870786667</v>
       </c>
       <c r="C410" s="1">
-        <v>0.0090428460389375687</v>
+        <v>0.16717864573001862</v>
       </c>
     </row>
     <row r="411">
@@ -4588,7 +4586,7 @@
         <v>-0.30431729555130005</v>
       </c>
       <c r="C411" s="1">
-        <v>0.063707500696182251</v>
+        <v>-0.0269591324031353</v>
       </c>
     </row>
     <row r="412">
@@ -4599,7 +4597,7 @@
         <v>0.10802441090345383</v>
       </c>
       <c r="C412" s="1">
-        <v>0.36767399311065674</v>
+        <v>0.15754611790180206</v>
       </c>
     </row>
     <row r="413">
@@ -4610,7 +4608,7 @@
         <v>0.40989306569099426</v>
       </c>
       <c r="C413" s="1">
-        <v>0.089158177375793457</v>
+        <v>0.08881513774394989</v>
       </c>
     </row>
     <row r="414">
@@ -4621,7 +4619,7 @@
         <v>0.61810970306396484</v>
       </c>
       <c r="C414" s="1">
-        <v>0.23537206649780273</v>
+        <v>0.23544614017009735</v>
       </c>
     </row>
     <row r="415">
@@ -4632,7 +4630,7 @@
         <v>-0.16747620701789856</v>
       </c>
       <c r="C415" s="1">
-        <v>-0.0016560518415644765</v>
+        <v>-0.03879079595208168</v>
       </c>
     </row>
     <row r="416">
@@ -4643,7 +4641,7 @@
         <v>0.13712017238140106</v>
       </c>
       <c r="C416" s="1">
-        <v>-0.073715247213840485</v>
+        <v>0.15235936641693115</v>
       </c>
     </row>
     <row r="417">
@@ -4654,7 +4652,7 @@
         <v>-0.020633475854992867</v>
       </c>
       <c r="C417" s="1">
-        <v>0.39249399304389954</v>
+        <v>0.51942211389541626</v>
       </c>
     </row>
     <row r="418">
@@ -4665,7 +4663,7 @@
         <v>0.20531339943408966</v>
       </c>
       <c r="C418" s="1">
-        <v>0.11433017253875732</v>
+        <v>0.0095068458467721939</v>
       </c>
     </row>
     <row r="419">
@@ -4676,7 +4674,7 @@
         <v>0.084838710725307465</v>
       </c>
       <c r="C419" s="1">
-        <v>0.38821369409561157</v>
+        <v>0.50166606903076172</v>
       </c>
     </row>
     <row r="420">
@@ -4687,7 +4685,7 @@
         <v>0.12802775204181671</v>
       </c>
       <c r="C420" s="1">
-        <v>-0.067632034420967102</v>
+        <v>-0.049215242266654968</v>
       </c>
     </row>
     <row r="421">
@@ -4698,7 +4696,7 @@
         <v>0.21076886355876923</v>
       </c>
       <c r="C421" s="1">
-        <v>-0.31751337647438049</v>
+        <v>-0.3016030490398407</v>
       </c>
     </row>
     <row r="422">
@@ -4709,7 +4707,7 @@
         <v>-0.16565772891044617</v>
       </c>
       <c r="C422" s="1">
-        <v>0.0041410960257053375</v>
+        <v>0.072244614362716675</v>
       </c>
     </row>
     <row r="423">
@@ -4720,7 +4718,7 @@
         <v>-0.18475182354450226</v>
       </c>
       <c r="C423" s="1">
-        <v>-0.34829223155975342</v>
+        <v>-0.53198480606079102</v>
       </c>
     </row>
     <row r="424">
@@ -4731,7 +4729,7 @@
         <v>0.24895705282688141</v>
       </c>
       <c r="C424" s="1">
-        <v>-0.077445521950721741</v>
+        <v>-0.11436504125595093</v>
       </c>
     </row>
     <row r="425">
@@ -4742,7 +4740,7 @@
         <v>0.05165133997797966</v>
       </c>
       <c r="C425" s="1">
-        <v>-0.1010613813996315</v>
+        <v>-0.070848844945430756</v>
       </c>
     </row>
     <row r="426">
@@ -4753,7 +4751,7 @@
         <v>-0.4338843822479248</v>
       </c>
       <c r="C426" s="1">
-        <v>-0.63988077640533447</v>
+        <v>-0.37334340810775757</v>
       </c>
     </row>
     <row r="427">
@@ -4764,7 +4762,7 @@
         <v>-0.22203078866004944</v>
       </c>
       <c r="C427" s="1">
-        <v>-0.25177213549613953</v>
+        <v>-0.12738339602947235</v>
       </c>
     </row>
     <row r="428">
@@ -4775,7 +4773,7 @@
         <v>0.2498663067817688</v>
       </c>
       <c r="C428" s="1">
-        <v>0.2033374160528183</v>
+        <v>0.39726594090461731</v>
       </c>
     </row>
     <row r="429">
@@ -4786,7 +4784,7 @@
         <v>-0.1438358873128891</v>
       </c>
       <c r="C429" s="1">
-        <v>0.29213359951972961</v>
+        <v>0.39842432737350464</v>
       </c>
     </row>
     <row r="430">
@@ -4797,7 +4795,7 @@
         <v>0.24577471613883972</v>
       </c>
       <c r="C430" s="1">
-        <v>-0.0044327229261398315</v>
+        <v>-0.060345638543367386</v>
       </c>
     </row>
     <row r="431">
@@ -4808,7 +4806,7 @@
         <v>0.18485543131828308</v>
       </c>
       <c r="C431" s="1">
-        <v>0.056010931730270386</v>
+        <v>0.13990952074527741</v>
       </c>
     </row>
     <row r="432">
@@ -4819,7 +4817,7 @@
         <v>-0.143381267786026</v>
       </c>
       <c r="C432" s="1">
-        <v>-0.23567898571491241</v>
+        <v>-0.19900067150592804</v>
       </c>
     </row>
     <row r="433">
@@ -4830,7 +4828,7 @@
         <v>0.43126031756401062</v>
       </c>
       <c r="C433" s="1">
-        <v>-0.13673239946365356</v>
+        <v>-0.29179194569587708</v>
       </c>
     </row>
     <row r="434">
@@ -4841,7 +4839,7 @@
         <v>-0.087462835013866425</v>
       </c>
       <c r="C434" s="1">
-        <v>0.17008063197135925</v>
+        <v>0.38182511925697327</v>
       </c>
     </row>
     <row r="435">
@@ -4852,7 +4850,7 @@
         <v>0.12029919028282166</v>
       </c>
       <c r="C435" s="1">
-        <v>0.12530441582202911</v>
+        <v>0.10273612290620804</v>
       </c>
     </row>
     <row r="436">
@@ -4863,7 +4861,7 @@
         <v>-0.019269609823822975</v>
       </c>
       <c r="C436" s="1">
-        <v>0.19951337575912476</v>
+        <v>0.20025686919689178</v>
       </c>
     </row>
     <row r="437">
@@ -4874,7 +4872,7 @@
         <v>-0.014723395928740501</v>
       </c>
       <c r="C437" s="1">
-        <v>0.3287079930305481</v>
+        <v>0.25807461142539978</v>
       </c>
     </row>
     <row r="438">
@@ -4885,7 +4883,7 @@
         <v>-0.14565438032150269</v>
       </c>
       <c r="C438" s="1">
-        <v>-0.089128829538822174</v>
+        <v>0.039845343679189682</v>
       </c>
     </row>
     <row r="439">
@@ -4896,7 +4894,7 @@
         <v>-0.25203579664230347</v>
       </c>
       <c r="C439" s="1">
-        <v>-0.095892012119293213</v>
+        <v>0.10481204092502594</v>
       </c>
     </row>
     <row r="440">
@@ -4904,10 +4902,10 @@
         <v>201107</v>
       </c>
       <c r="B440" s="1">
-        <v>-0.097919128835201263</v>
+        <v>-0.097919128835201264</v>
       </c>
       <c r="C440" s="1">
-        <v>-0.089170798659324646</v>
+        <v>0.079260587692260742</v>
       </c>
     </row>
     <row r="441">
@@ -4918,7 +4916,7 @@
         <v>-0.4170633852481842</v>
       </c>
       <c r="C441" s="1">
-        <v>-0.046250604093074799</v>
+        <v>0.20047576725482941</v>
       </c>
     </row>
     <row r="442">
@@ -4929,7 +4927,7 @@
         <v>-0.36841890215873718</v>
       </c>
       <c r="C442" s="1">
-        <v>-0.41789135336875916</v>
+        <v>-0.51080065965652466</v>
       </c>
     </row>
     <row r="443">
@@ -4940,7 +4938,7 @@
         <v>0.38807123899459839</v>
       </c>
       <c r="C443" s="1">
-        <v>-0.075697213411331177</v>
+        <v>0.035003788769245148</v>
       </c>
     </row>
     <row r="444">
@@ -4951,7 +4949,7 @@
         <v>-0.052911598235368729</v>
       </c>
       <c r="C444" s="1">
-        <v>-0.020189609378576279</v>
+        <v>-0.18790440261363983</v>
       </c>
     </row>
     <row r="445">
@@ -4962,7 +4960,7 @@
         <v>0.013463134877383709</v>
       </c>
       <c r="C445" s="1">
-        <v>-0.29797601699829102</v>
+        <v>-0.22984881699085236</v>
       </c>
     </row>
     <row r="446">
@@ -4973,7 +4971,7 @@
         <v>0.063926123082637787</v>
       </c>
       <c r="C446" s="1">
-        <v>-0.24555203318595886</v>
+        <v>-0.071776479482650757</v>
       </c>
     </row>
     <row r="447">
@@ -4984,7 +4982,7 @@
         <v>0.30896711349487305</v>
       </c>
       <c r="C447" s="1">
-        <v>0.26674231886863708</v>
+        <v>0.076520919799804688</v>
       </c>
     </row>
     <row r="448">
@@ -4995,7 +4993,7 @@
         <v>-0.10473845154047012</v>
       </c>
       <c r="C448" s="1">
-        <v>-0.066318057477474213</v>
+        <v>0.036396231502294541</v>
       </c>
     </row>
     <row r="449">
@@ -5006,7 +5004,7 @@
         <v>-0.10246533900499344</v>
       </c>
       <c r="C449" s="1">
-        <v>-0.12522046267986298</v>
+        <v>-0.040022347122430801</v>
       </c>
     </row>
     <row r="450">
@@ -5017,7 +5015,7 @@
         <v>-0.41797265410423279</v>
       </c>
       <c r="C450" s="1">
-        <v>-0.036471158266067505</v>
+        <v>-0.19855695962905884</v>
       </c>
     </row>
     <row r="451">
@@ -5025,10 +5023,10 @@
         <v>201206</v>
       </c>
       <c r="B451" s="1">
-        <v>0.16121512651443481</v>
+        <v>0.16121512651443482</v>
       </c>
       <c r="C451" s="1">
-        <v>-0.27624607086181641</v>
+        <v>-0.047920383512973786</v>
       </c>
     </row>
     <row r="452">
@@ -5039,7 +5037,7 @@
         <v>0.10438743978738785</v>
       </c>
       <c r="C452" s="1">
-        <v>-0.093511216342449188</v>
+        <v>0.092664562165737152</v>
       </c>
     </row>
     <row r="453">
@@ -5050,7 +5048,7 @@
         <v>0.07574627548456192</v>
       </c>
       <c r="C453" s="1">
-        <v>0.15983575582504272</v>
+        <v>0.34901848435401917</v>
       </c>
     </row>
     <row r="454">
@@ -5061,7 +5059,7 @@
         <v>0.030738752335309982</v>
       </c>
       <c r="C454" s="1">
-        <v>0.29381981492042542</v>
+        <v>0.080573722720146179</v>
       </c>
     </row>
     <row r="455">
@@ -5072,7 +5070,7 @@
         <v>-0.12792414426803589</v>
       </c>
       <c r="C455" s="1">
-        <v>-0.073397263884544373</v>
+        <v>-0.051331888884305954</v>
       </c>
     </row>
     <row r="456">
@@ -5083,7 +5081,7 @@
         <v>-0.060185544192790985</v>
       </c>
       <c r="C456" s="1">
-        <v>-0.047434046864509583</v>
+        <v>0.0054809087887406349</v>
       </c>
     </row>
     <row r="457">
@@ -5094,7 +5092,7 @@
         <v>-0.013814150355756283</v>
       </c>
       <c r="C457" s="1">
-        <v>0.094900608062744141</v>
+        <v>0.10922035574913025</v>
       </c>
     </row>
     <row r="458">
@@ -5105,7 +5103,7 @@
         <v>0.17621763050556183</v>
       </c>
       <c r="C458" s="1">
-        <v>0.0094327088445425034</v>
+        <v>0.14426149427890778</v>
       </c>
     </row>
     <row r="459">
@@ -5116,7 +5114,7 @@
         <v>-0.006540209986269474</v>
       </c>
       <c r="C459" s="1">
-        <v>-0.038226708769798279</v>
+        <v>-0.10604313015937805</v>
       </c>
     </row>
     <row r="460">
@@ -5127,7 +5125,7 @@
         <v>-0.050183869898319244</v>
       </c>
       <c r="C460" s="1">
-        <v>-0.45689889788627625</v>
+        <v>-0.41983777284622192</v>
       </c>
     </row>
     <row r="461">
@@ -5138,7 +5136,7 @@
         <v>-0.0038124816492199898</v>
       </c>
       <c r="C461" s="1">
-        <v>-0.17720155417919159</v>
+        <v>-0.19041509926319122</v>
       </c>
     </row>
     <row r="462">
@@ -5149,7 +5147,7 @@
         <v>0.062562264502048492</v>
       </c>
       <c r="C462" s="1">
-        <v>-0.18615147471427917</v>
+        <v>-0.10361086577177048</v>
       </c>
     </row>
     <row r="463">
@@ -5160,7 +5158,7 @@
         <v>-0.23203246295452118</v>
       </c>
       <c r="C463" s="1">
-        <v>-0.093016050755977631</v>
+        <v>0.070987366139888764</v>
       </c>
     </row>
     <row r="464">
@@ -5171,7 +5169,7 @@
         <v>0.16712521016597748</v>
       </c>
       <c r="C464" s="1">
-        <v>-0.45110365748405457</v>
+        <v>-0.43087506294250488</v>
       </c>
     </row>
     <row r="465">
@@ -5182,7 +5180,7 @@
         <v>-0.0042671025730669498</v>
       </c>
       <c r="C465" s="1">
-        <v>0.13655400276184082</v>
+        <v>0.24126154184341431</v>
       </c>
     </row>
     <row r="466">
@@ -5193,7 +5191,7 @@
         <v>0.022100949659943581</v>
       </c>
       <c r="C466" s="1">
-        <v>-0.073745653033256531</v>
+        <v>-0.093990378081798554</v>
       </c>
     </row>
     <row r="467">
@@ -5204,7 +5202,7 @@
         <v>0.19167476892471313</v>
       </c>
       <c r="C467" s="1">
-        <v>-0.028504719957709312</v>
+        <v>-0.0031292061321437359</v>
       </c>
     </row>
     <row r="468">
@@ -5215,7 +5213,7 @@
         <v>0.022555571049451828</v>
       </c>
       <c r="C468" s="1">
-        <v>-0.36161452531814575</v>
+        <v>-0.25806045532226563</v>
       </c>
     </row>
     <row r="469">
@@ -5226,7 +5224,7 @@
         <v>0.014827001839876175</v>
       </c>
       <c r="C469" s="1">
-        <v>-0.15765205025672913</v>
+        <v>-0.027143491432070732</v>
       </c>
     </row>
     <row r="470">
@@ -5237,7 +5235,7 @@
         <v>-0.15247370302677155</v>
       </c>
       <c r="C470" s="1">
-        <v>0.14796307682991028</v>
+        <v>-0.034784410148859024</v>
       </c>
     </row>
     <row r="471">
@@ -5248,7 +5246,7 @@
         <v>0.099386587738990784</v>
       </c>
       <c r="C471" s="1">
-        <v>-0.057165209203958511</v>
+        <v>-0.10373854637145996</v>
       </c>
     </row>
     <row r="472">
@@ -5259,7 +5257,7 @@
         <v>0.017100108787417412</v>
       </c>
       <c r="C472" s="1">
-        <v>0.12072250247001648</v>
+        <v>0.16796496510505676</v>
       </c>
     </row>
     <row r="473">
@@ -5270,7 +5268,7 @@
         <v>0.093931138515472412</v>
       </c>
       <c r="C473" s="1">
-        <v>-0.030163124203681946</v>
+        <v>-0.047532510012388229</v>
       </c>
     </row>
     <row r="474">
@@ -5281,7 +5279,7 @@
         <v>0.180763840675354</v>
       </c>
       <c r="C474" s="1">
-        <v>0.048213448375463486</v>
+        <v>0.085981264710426331</v>
       </c>
     </row>
     <row r="475">
@@ -5292,7 +5290,7 @@
         <v>0.060743778944015503</v>
       </c>
       <c r="C475" s="1">
-        <v>-0.36845970153808594</v>
+        <v>-0.16323663294315338</v>
       </c>
     </row>
     <row r="476">
@@ -5303,7 +5301,7 @@
         <v>-0.11928633600473404</v>
       </c>
       <c r="C476" s="1">
-        <v>-0.25153401494026184</v>
+        <v>-0.34250342845916748</v>
       </c>
     </row>
     <row r="477">
@@ -5314,7 +5312,7 @@
         <v>-0.077461160719394684</v>
       </c>
       <c r="C477" s="1">
-        <v>-0.1037023663520813</v>
+        <v>0.088005229830741882</v>
       </c>
     </row>
     <row r="478">
@@ -5325,7 +5323,7 @@
         <v>-0.091099806129932404</v>
       </c>
       <c r="C478" s="1">
-        <v>-0.34714001417160034</v>
+        <v>-0.36608129739761353</v>
       </c>
     </row>
     <row r="479">
@@ -5336,7 +5334,7 @@
         <v>-0.28613242506980896</v>
       </c>
       <c r="C479" s="1">
-        <v>-0.40537071228027344</v>
+        <v>-0.31285619735717773</v>
       </c>
     </row>
     <row r="480">
@@ -5347,7 +5345,7 @@
         <v>-0.31886515021324158</v>
       </c>
       <c r="C480" s="1">
-        <v>-0.079020515084266663</v>
+        <v>-0.25502672791481018</v>
       </c>
     </row>
     <row r="481">
@@ -5358,7 +5356,7 @@
         <v>-0.01245028804987669</v>
       </c>
       <c r="C481" s="1">
-        <v>-0.51019847393035889</v>
+        <v>-0.6566498875617981</v>
       </c>
     </row>
     <row r="482">
@@ -5369,7 +5367,7 @@
         <v>0.063926123082637787</v>
       </c>
       <c r="C482" s="1">
-        <v>-0.263355553150177</v>
+        <v>-0.42878228425979614</v>
       </c>
     </row>
     <row r="483">
@@ -5380,7 +5378,7 @@
         <v>0.15485043823719025</v>
       </c>
       <c r="C483" s="1">
-        <v>-0.028465030714869499</v>
+        <v>0.00046842169831506908</v>
       </c>
     </row>
     <row r="484">
@@ -5388,10 +5386,10 @@
         <v>201503</v>
       </c>
       <c r="B484" s="1">
-        <v>-0.056093949824571609</v>
+        <v>-0.05609394982457161</v>
       </c>
       <c r="C484" s="1">
-        <v>-0.59852051734924316</v>
+        <v>-0.54857462644577026</v>
       </c>
     </row>
     <row r="485">
@@ -5402,7 +5400,7 @@
         <v>0.19212938845157623</v>
       </c>
       <c r="C485" s="1">
-        <v>0.11071667820215225</v>
+        <v>0.069297797977924347</v>
       </c>
     </row>
     <row r="486">
@@ -5413,7 +5411,7 @@
         <v>-0.062004029750823975</v>
       </c>
       <c r="C486" s="1">
-        <v>0.30706331133842468</v>
+        <v>0.34613135457038879</v>
       </c>
     </row>
     <row r="487">
@@ -5424,7 +5422,7 @@
         <v>-0.18338796496391296</v>
       </c>
       <c r="C487" s="1">
-        <v>-0.46291708946228027</v>
+        <v>-0.40140846371650696</v>
       </c>
     </row>
     <row r="488">
@@ -5435,7 +5433,7 @@
         <v>-0.024270445108413696</v>
       </c>
       <c r="C488" s="1">
-        <v>-0.12687940895557404</v>
+        <v>-0.30069458484649658</v>
       </c>
     </row>
     <row r="489">
@@ -5443,10 +5441,10 @@
         <v>201508</v>
       </c>
       <c r="B489" s="1">
-        <v>-0.38387602567672729</v>
+        <v>-0.3838760256767273</v>
       </c>
       <c r="C489" s="1">
-        <v>-0.25351360440254211</v>
+        <v>-0.097367621958255768</v>
       </c>
     </row>
     <row r="490">
@@ -5457,7 +5455,7 @@
         <v>-0.15065522491931915</v>
       </c>
       <c r="C490" s="1">
-        <v>-0.14662562310695648</v>
+        <v>-0.20136791467666626</v>
       </c>
     </row>
     <row r="491">
@@ -5468,7 +5466,7 @@
         <v>0.18803776800632477</v>
       </c>
       <c r="C491" s="1">
-        <v>0.016716605052351952</v>
+        <v>-0.006611816119402647</v>
       </c>
     </row>
     <row r="492">
@@ -5479,7 +5477,7 @@
         <v>0.042558908462524414</v>
       </c>
       <c r="C492" s="1">
-        <v>-0.49976459145545959</v>
+        <v>-0.4657149612903595</v>
       </c>
     </row>
     <row r="493">
@@ -5490,7 +5488,7 @@
         <v>-0.227486252784729</v>
       </c>
       <c r="C493" s="1">
-        <v>-0.11053238064050674</v>
+        <v>0.092946350574493408</v>
       </c>
     </row>
     <row r="494">
@@ -5501,7 +5499,7 @@
         <v>-0.36114498972892761</v>
       </c>
       <c r="C494" s="1">
-        <v>-0.17972548305988312</v>
+        <v>-0.22325757145881653</v>
       </c>
     </row>
     <row r="495">
@@ -5512,7 +5510,7 @@
         <v>0.053469829261302948</v>
       </c>
       <c r="C495" s="1">
-        <v>0.17040202021598816</v>
+        <v>0.11203596740961075</v>
       </c>
     </row>
     <row r="496">
@@ -5523,7 +5521,7 @@
         <v>0.043013527989387512</v>
       </c>
       <c r="C496" s="1">
-        <v>0.037940420210361481</v>
+        <v>0.02297399751842022</v>
       </c>
     </row>
     <row r="497">
@@ -5534,7 +5532,7 @@
         <v>0.20076718926429749</v>
       </c>
       <c r="C497" s="1">
-        <v>0.19436435401439667</v>
+        <v>0.18076540529727936</v>
       </c>
     </row>
     <row r="498">
@@ -5545,7 +5543,7 @@
         <v>0.0034614624455571175</v>
       </c>
       <c r="C498" s="1">
-        <v>-0.083404980599880219</v>
+        <v>-0.058936424553394318</v>
       </c>
     </row>
     <row r="499">
@@ -5556,7 +5554,7 @@
         <v>-0.08518972247838974</v>
       </c>
       <c r="C499" s="1">
-        <v>-0.087442688643932343</v>
+        <v>-0.1545722484588623</v>
       </c>
     </row>
     <row r="500">
@@ -5567,7 +5565,7 @@
         <v>-0.026088932529091835</v>
       </c>
       <c r="C500" s="1">
-        <v>-0.32302173972129822</v>
+        <v>-0.36543574929237366</v>
       </c>
     </row>
     <row r="501">
@@ -5578,7 +5576,7 @@
         <v>-0.010177180171012878</v>
       </c>
       <c r="C501" s="1">
-        <v>0.2126934677362442</v>
+        <v>0.41848373413085938</v>
       </c>
     </row>
     <row r="502">
@@ -5589,7 +5587,7 @@
         <v>-0.0079040722921490669</v>
       </c>
       <c r="C502" s="1">
-        <v>0.13371121883392334</v>
+        <v>0.12318515032529831</v>
       </c>
     </row>
     <row r="503">
@@ -5600,7 +5598,7 @@
         <v>0.084838710725307465</v>
       </c>
       <c r="C503" s="1">
-        <v>-0.29694360494613647</v>
+        <v>-0.26404267549514771</v>
       </c>
     </row>
     <row r="504">
@@ -5611,7 +5609,7 @@
         <v>0.11893532425165176</v>
       </c>
       <c r="C504" s="1">
-        <v>-0.37623003125190735</v>
+        <v>-0.31565076112747192</v>
       </c>
     </row>
     <row r="505">
@@ -5622,7 +5620,7 @@
         <v>0.17667225003242493</v>
       </c>
       <c r="C505" s="1">
-        <v>-0.25318208336830139</v>
+        <v>-0.052927769720554352</v>
       </c>
     </row>
     <row r="506">
@@ -5633,7 +5631,7 @@
         <v>-0.024725068360567093</v>
       </c>
       <c r="C506" s="1">
-        <v>0.015896638855338097</v>
+        <v>0.12865696847438812</v>
       </c>
     </row>
     <row r="507">
@@ -5644,7 +5642,7 @@
         <v>-0.066550247371196747</v>
       </c>
       <c r="C507" s="1">
-        <v>0.12264146655797958</v>
+        <v>0.11867841333150864</v>
       </c>
     </row>
     <row r="508">
@@ -5655,7 +5653,7 @@
         <v>-0.091099806129932404</v>
       </c>
       <c r="C508" s="1">
-        <v>-0.2912503182888031</v>
+        <v>-0.24963153898715973</v>
       </c>
     </row>
     <row r="509">
@@ -5666,7 +5664,7 @@
         <v>-0.0069948309101164341</v>
       </c>
       <c r="C509" s="1">
-        <v>-0.16876673698425293</v>
+        <v>-0.11667894572019577</v>
       </c>
     </row>
     <row r="510">
@@ -5677,7 +5675,7 @@
         <v>0.042558908462524414</v>
       </c>
       <c r="C510" s="1">
-        <v>0.024003230035305023</v>
+        <v>0.062585130333900452</v>
       </c>
     </row>
     <row r="511">
@@ -5688,7 +5686,7 @@
         <v>-0.13792581856250763</v>
       </c>
       <c r="C511" s="1">
-        <v>-0.012625209987163544</v>
+        <v>-0.013481887988746166</v>
       </c>
     </row>
     <row r="512">
@@ -5699,7 +5697,7 @@
         <v>0.19167476892471313</v>
       </c>
       <c r="C512" s="1">
-        <v>0.22935347259044647</v>
+        <v>0.22923155128955841</v>
       </c>
     </row>
     <row r="513">
@@ -5710,7 +5708,7 @@
         <v>-0.0069948309101164341</v>
       </c>
       <c r="C513" s="1">
-        <v>0.23572574555873871</v>
+        <v>0.5010492205619812</v>
       </c>
     </row>
     <row r="514">
@@ -5721,7 +5719,7 @@
         <v>0.21395121514797211</v>
       </c>
       <c r="C514" s="1">
-        <v>-0.021020509302616119</v>
+        <v>-0.070690661668777466</v>
       </c>
     </row>
     <row r="515">
@@ -5732,7 +5730,7 @@
         <v>0.10256894677877426</v>
       </c>
       <c r="C515" s="1">
-        <v>-0.24854198098182678</v>
+        <v>-0.18498559296131134</v>
       </c>
     </row>
     <row r="516">
@@ -5743,7 +5741,7 @@
         <v>-0.084280483424663544</v>
       </c>
       <c r="C516" s="1">
-        <v>-0.28839111328125</v>
+        <v>-0.20557890832424164</v>
       </c>
     </row>
     <row r="517">
@@ -5754,7 +5752,7 @@
         <v>0.060743778944015503</v>
       </c>
       <c r="C517" s="1">
-        <v>0.054409105330705643</v>
+        <v>-0.12005047500133514</v>
       </c>
     </row>
     <row r="518">
@@ -5765,7 +5763,7 @@
         <v>-0.036545224487781525</v>
       </c>
       <c r="C518" s="1">
-        <v>0.35934680700302124</v>
+        <v>0.4503403902053833</v>
       </c>
     </row>
     <row r="519">
@@ -5776,7 +5774,7 @@
         <v>-0.0015393695794045925</v>
       </c>
       <c r="C519" s="1">
-        <v>0.040742795914411545</v>
+        <v>-0.10305886715650558</v>
       </c>
     </row>
     <row r="520">
@@ -5787,7 +5785,7 @@
         <v>-0.11337625235319138</v>
       </c>
       <c r="C520" s="1">
-        <v>0.034949999302625656</v>
+        <v>0.05720241367816925</v>
       </c>
     </row>
     <row r="521">
@@ -5798,7 +5796,7 @@
         <v>0.27577972412109375</v>
       </c>
       <c r="C521" s="1">
-        <v>-0.18054111301898956</v>
+        <v>-0.17925083637237549</v>
       </c>
     </row>
     <row r="522">
@@ -5809,7 +5807,7 @@
         <v>0.059379909187555313</v>
       </c>
       <c r="C522" s="1">
-        <v>-0.41387367248535156</v>
+        <v>-0.33811917901039124</v>
       </c>
     </row>
     <row r="523">
@@ -5820,7 +5818,7 @@
         <v>-0.019269609823822975</v>
       </c>
       <c r="C523" s="1">
-        <v>-0.17640078067779541</v>
+        <v>-0.2043631374835968</v>
       </c>
     </row>
     <row r="524">
@@ -5831,7 +5829,7 @@
         <v>0.01028078980743885</v>
       </c>
       <c r="C524" s="1">
-        <v>-0.056241985410451889</v>
+        <v>-0.15477313101291657</v>
       </c>
     </row>
     <row r="525">
@@ -5842,7 +5840,7 @@
         <v>-0.0042671025730669498</v>
       </c>
       <c r="C525" s="1">
-        <v>-0.36975911259651184</v>
+        <v>-0.16541232168674469</v>
       </c>
     </row>
     <row r="526">
@@ -5853,7 +5851,7 @@
         <v>0.12757314741611481</v>
       </c>
       <c r="C526" s="1">
-        <v>0.061972614377737045</v>
+        <v>0.010775282979011536</v>
       </c>
     </row>
     <row r="527">
@@ -5864,7 +5862,7 @@
         <v>-0.28204083442687988</v>
       </c>
       <c r="C527" s="1">
-        <v>-0.076122894883155823</v>
+        <v>0.064033575356006622</v>
       </c>
     </row>
     <row r="528">
@@ -5875,7 +5873,7 @@
         <v>-0.22475850582122803</v>
       </c>
       <c r="C528" s="1">
-        <v>-0.25575336813926697</v>
+        <v>-0.27217575907707214</v>
       </c>
     </row>
     <row r="529">
@@ -5886,7 +5884,7 @@
         <v>-0.35705339908599854</v>
       </c>
       <c r="C529" s="1">
-        <v>0.078507855534553528</v>
+        <v>-0.10174655914306641</v>
       </c>
     </row>
     <row r="530">
@@ -5894,10 +5892,10 @@
         <v>201901</v>
       </c>
       <c r="B530" s="1">
-        <v>0.17394451797008514</v>
+        <v>0.17394451797008515</v>
       </c>
       <c r="C530" s="1">
-        <v>-0.019239991903305054</v>
+        <v>0.18367248773574829</v>
       </c>
     </row>
     <row r="531">
@@ -5908,7 +5906,7 @@
         <v>0.10484205186367035</v>
       </c>
       <c r="C531" s="1">
-        <v>-0.061057034879922867</v>
+        <v>-0.17258259654045105</v>
       </c>
     </row>
     <row r="532">
@@ -5919,7 +5917,7 @@
         <v>-0.053366221487522125</v>
       </c>
       <c r="C532" s="1">
-        <v>-0.096943683922290802</v>
+        <v>-0.057760260999202728</v>
       </c>
     </row>
     <row r="533">
@@ -5930,7 +5928,7 @@
         <v>0.049378234893083572</v>
       </c>
       <c r="C533" s="1">
-        <v>-0.06933748722076416</v>
+        <v>-0.067915908992290497</v>
       </c>
     </row>
     <row r="534">
@@ -5941,7 +5939,7 @@
         <v>-0.25339967012405396</v>
       </c>
       <c r="C534" s="1">
-        <v>-0.24126912653446198</v>
+        <v>-0.063419722020626068</v>
       </c>
     </row>
     <row r="535">
@@ -5952,7 +5950,7 @@
         <v>0.014372376725077629</v>
       </c>
       <c r="C535" s="1">
-        <v>0.077460892498493195</v>
+        <v>0.14288961887359619</v>
       </c>
     </row>
     <row r="536">
@@ -5960,10 +5958,10 @@
         <v>201907</v>
       </c>
       <c r="B536" s="1">
-        <v>-0.097919128835201263</v>
+        <v>-0.097919128835201264</v>
       </c>
       <c r="C536" s="1">
-        <v>-0.044009018689393997</v>
+        <v>-0.12643828988075256</v>
       </c>
     </row>
     <row r="537">
@@ -5974,7 +5972,7 @@
         <v>-0.061549406498670578</v>
       </c>
       <c r="C537" s="1">
-        <v>-0.41452211141586304</v>
+        <v>-0.12968780100345612</v>
       </c>
     </row>
     <row r="538">
@@ -5985,7 +5983,7 @@
         <v>0.10847902297973633</v>
       </c>
       <c r="C538" s="1">
-        <v>-0.17100968956947327</v>
+        <v>-0.19199110567569733</v>
       </c>
     </row>
     <row r="539">
@@ -5996,7 +5994,7 @@
         <v>-0.020178850740194321</v>
       </c>
       <c r="C539" s="1">
-        <v>-0.27573400735855103</v>
+        <v>-0.18951819837093353</v>
       </c>
     </row>
     <row r="540">
@@ -6007,7 +6005,7 @@
         <v>-0.01836036704480648</v>
       </c>
       <c r="C540" s="1">
-        <v>-0.14410111308097839</v>
+        <v>-0.10495894402265549</v>
       </c>
     </row>
     <row r="541">
@@ -6018,7 +6016,7 @@
         <v>0.0952950119972229</v>
       </c>
       <c r="C541" s="1">
-        <v>0.015020988881587982</v>
+        <v>0.17442674934864044</v>
       </c>
     </row>
     <row r="542">
@@ -6029,7 +6027,7 @@
         <v>-0.14156278967857361</v>
       </c>
       <c r="C542" s="1">
-        <v>0.34337490797042847</v>
+        <v>0.14343850314617157</v>
       </c>
     </row>
     <row r="543">
@@ -6040,7 +6038,7 @@
         <v>-0.48752972483634949</v>
       </c>
       <c r="C543" s="1">
-        <v>-0.46028724312782288</v>
+        <v>-0.31420925259590149</v>
       </c>
     </row>
     <row r="544">
@@ -6051,7 +6049,7 @@
         <v>-0.71393120288848877</v>
       </c>
       <c r="C544" s="1">
-        <v>-0.71830588579177856</v>
+        <v>-0.84308338165283203</v>
       </c>
     </row>
     <row r="545">
@@ -6062,7 +6060,7 @@
         <v>0.35988473892211914</v>
       </c>
       <c r="C545" s="1">
-        <v>-0.29009300470352173</v>
+        <v>-0.29027873277664185</v>
       </c>
     </row>
     <row r="546">
@@ -6073,7 +6071,7 @@
         <v>0.07756476104259491</v>
       </c>
       <c r="C546" s="1">
-        <v>0.28110718727111816</v>
+        <v>0.31793871521949768</v>
       </c>
     </row>
     <row r="547">
@@ -6081,10 +6079,10 @@
         <v>202006</v>
       </c>
       <c r="B547" s="1">
-        <v>-0.056093949824571609</v>
+        <v>-0.05609394982457161</v>
       </c>
       <c r="C547" s="1">
-        <v>0.48458263278007507</v>
+        <v>0.50464820861816406</v>
       </c>
     </row>
     <row r="548">
@@ -6095,7 +6093,7 @@
         <v>0.12620927393436432</v>
       </c>
       <c r="C548" s="1">
-        <v>0.15910585224628448</v>
+        <v>0.078125864267349243</v>
       </c>
     </row>
     <row r="549">
@@ -6106,7 +6104,7 @@
         <v>0.13211934268474579</v>
       </c>
       <c r="C549" s="1">
-        <v>0.25559413433074951</v>
+        <v>0.41061019897460938</v>
       </c>
     </row>
     <row r="550">
@@ -6117,7 +6115,7 @@
         <v>-0.077915780246257782</v>
       </c>
       <c r="C550" s="1">
-        <v>-0.28006482124328613</v>
+        <v>-0.26018041372299194</v>
       </c>
     </row>
     <row r="551">
@@ -6128,7 +6126,7 @@
         <v>-0.27112993597984314</v>
       </c>
       <c r="C551" s="1">
-        <v>-0.069406531751155853</v>
+        <v>-0.053980842232704163</v>
       </c>
     </row>
     <row r="552">
@@ -6139,7 +6137,7 @@
         <v>0.59356015920639038</v>
       </c>
       <c r="C552" s="1">
-        <v>-0.01384331937879324</v>
+        <v>0.2488260418176651</v>
       </c>
     </row>
     <row r="553">
@@ -6150,7 +6148,7 @@
         <v>0.16712521016597748</v>
       </c>
       <c r="C553" s="1">
-        <v>0.22174482047557831</v>
+        <v>0.19468499720096588</v>
       </c>
     </row>
     <row r="554">
@@ -6161,7 +6159,7 @@
         <v>-0.039727576076984406</v>
       </c>
       <c r="C554" s="1">
-        <v>0.16772681474685669</v>
+        <v>-0.009318188764154911</v>
       </c>
     </row>
     <row r="555">
@@ -6172,7 +6170,7 @@
         <v>0.1475764662027359</v>
       </c>
       <c r="C555" s="1">
-        <v>-0.041831914335489273</v>
+        <v>-0.12334304302930832</v>
       </c>
     </row>
     <row r="556">
@@ -6183,7 +6181,7 @@
         <v>0.14121177792549133</v>
       </c>
       <c r="C556" s="1">
-        <v>-0.17694927752017975</v>
+        <v>-0.023519750684499741</v>
       </c>
     </row>
     <row r="557">
@@ -6194,7 +6192,7 @@
         <v>0.012553893961012363</v>
       </c>
       <c r="C557" s="1">
-        <v>0.10464823991060257</v>
+        <v>0.11400765180587769</v>
       </c>
     </row>
     <row r="558">
@@ -6205,7 +6203,7 @@
         <v>0.061653017997741699</v>
       </c>
       <c r="C558" s="1">
-        <v>0.037096910178661346</v>
+        <v>0.14904674887657166</v>
       </c>
     </row>
     <row r="559">
@@ -6216,7 +6214,7 @@
         <v>-0.0069948309101164341</v>
       </c>
       <c r="C559" s="1">
-        <v>-0.29598450660705566</v>
+        <v>-0.27730771899223328</v>
       </c>
     </row>
     <row r="560">
@@ -6227,7 +6225,7 @@
         <v>-0.050183869898319244</v>
       </c>
       <c r="C560" s="1">
-        <v>-0.45188799500465393</v>
+        <v>-0.54575538635253906</v>
       </c>
     </row>
     <row r="561">
@@ -6238,7 +6236,7 @@
         <v>0.039831183850765228</v>
       </c>
       <c r="C561" s="1">
-        <v>0.039987124502658844</v>
+        <v>-0.1418645977973938</v>
       </c>
     </row>
     <row r="562">
@@ -6249,7 +6247,7 @@
         <v>0.11529836058616638</v>
       </c>
       <c r="C562" s="1">
-        <v>-0.0018096982967108488</v>
+        <v>-0.14827843010425568</v>
       </c>
     </row>
     <row r="563">
@@ -6260,7 +6258,7 @@
         <v>0.03437572717666626</v>
       </c>
       <c r="C563" s="1">
-        <v>0.27190780639648438</v>
+        <v>0.38529232144355774</v>
       </c>
     </row>
     <row r="564">
@@ -6271,7 +6269,7 @@
         <v>-0.068368732929229736</v>
       </c>
       <c r="C564" s="1">
-        <v>-0.31970888376235962</v>
+        <v>-0.40696784853935242</v>
       </c>
     </row>
     <row r="565">
@@ -6282,7 +6280,7 @@
         <v>0.045741260051727295</v>
       </c>
       <c r="C565" s="1">
-        <v>-0.42303270101547241</v>
+        <v>-0.47519847750663757</v>
       </c>
     </row>
     <row r="566">
@@ -6293,7 +6291,7 @@
         <v>-0.1770232617855072</v>
       </c>
       <c r="C566" s="1">
-        <v>0.12628859281539917</v>
+        <v>0.42470654845237732</v>
       </c>
     </row>
     <row r="567">
@@ -6304,7 +6302,7 @@
         <v>0.085747949779033661</v>
       </c>
       <c r="C567" s="1">
-        <v>-0.10306554287672043</v>
+        <v>-0.27105420827865601</v>
       </c>
     </row>
     <row r="568">
@@ -6315,7 +6313,7 @@
         <v>0.25986796617507935</v>
       </c>
       <c r="C568" s="1">
-        <v>-0.11636904627084732</v>
+        <v>-0.16832390427589417</v>
       </c>
     </row>
     <row r="569">
@@ -6326,7 +6324,7 @@
         <v>-0.14883673191070557</v>
       </c>
       <c r="C569" s="1">
-        <v>-0.15347582101821899</v>
+        <v>-0.3468872606754303</v>
       </c>
     </row>
     <row r="570">
@@ -6337,7 +6335,7 @@
         <v>0.17985460162162781</v>
       </c>
       <c r="C570" s="1">
-        <v>-0.85544836521148682</v>
+        <v>-0.74777048826217651</v>
       </c>
     </row>
     <row r="571">
@@ -6348,7 +6346,7 @@
         <v>-0.44934150576591492</v>
       </c>
       <c r="C571" s="1">
-        <v>-0.14008383452892303</v>
+        <v>-0.27925562858581543</v>
       </c>
     </row>
     <row r="572">
@@ -6359,7 +6357,7 @@
         <v>0.24077390134334564</v>
       </c>
       <c r="C572" s="1">
-        <v>-0.42457672953605652</v>
+        <v>-0.63075578212738037</v>
       </c>
     </row>
     <row r="573">
@@ -6370,7 +6368,7 @@
         <v>-0.039727576076984406</v>
       </c>
       <c r="C573" s="1">
-        <v>0.19999657571315765</v>
+        <v>0.36350587010383606</v>
       </c>
     </row>
     <row r="574">
@@ -6381,7 +6379,7 @@
         <v>-0.54663056135177612</v>
       </c>
       <c r="C574" s="1">
-        <v>-0.59593474864959717</v>
+        <v>-0.80083757638931275</v>
       </c>
     </row>
     <row r="575">
@@ -6392,7 +6390,7 @@
         <v>0.25895875692367554</v>
       </c>
       <c r="C575" s="1">
-        <v>-0.35008719563484192</v>
+        <v>-0.33731552958488464</v>
       </c>
     </row>
     <row r="576">
@@ -6403,7 +6401,7 @@
         <v>0.084384091198444366</v>
       </c>
       <c r="C576" s="1">
-        <v>0.3464013934135437</v>
+        <v>0.45102390646934509</v>
       </c>
     </row>
     <row r="577">
@@ -6414,7 +6412,7 @@
         <v>-0.17156781256198883</v>
       </c>
       <c r="C577" s="1">
-        <v>0.23288719356060028</v>
+        <v>0.29606863856315613</v>
       </c>
     </row>
     <row r="578">
@@ -6422,10 +6420,10 @@
         <v>202301</v>
       </c>
       <c r="B578" s="1">
-        <v>-0.048820007592439651</v>
+        <v>-0.048820007592439652</v>
       </c>
       <c r="C578" s="1">
-        <v>-0.14546401798725128</v>
+        <v>-0.090597487986087799</v>
       </c>
     </row>
     <row r="579">
@@ -6436,7 +6434,7 @@
         <v>0.13211934268474579</v>
       </c>
       <c r="C579" s="1">
-        <v>-0.37642356753349304</v>
+        <v>-0.35308721661567688</v>
       </c>
     </row>
     <row r="580">
@@ -6447,7 +6445,7 @@
         <v>-0.24567112326622009</v>
       </c>
       <c r="C580" s="1">
-        <v>-0.38213652372360229</v>
+        <v>-0.45859327912330628</v>
       </c>
     </row>
     <row r="581">
@@ -6458,7 +6456,7 @@
         <v>0.088930301368236542</v>
       </c>
       <c r="C581" s="1">
-        <v>-0.071488156914710999</v>
+        <v>-0.24596861004829407</v>
       </c>
     </row>
     <row r="582">
@@ -6469,7 +6467,7 @@
         <v>-0.17202243208885193</v>
       </c>
       <c r="C582" s="1">
-        <v>-0.2788081169128418</v>
+        <v>-0.30027756094932556</v>
       </c>
     </row>
     <row r="583">
@@ -6480,7 +6478,7 @@
         <v>0.053469829261302948</v>
       </c>
       <c r="C583" s="1">
-        <v>-0.073764786124229431</v>
+        <v>-0.1312333345413208</v>
       </c>
     </row>
     <row r="584">
@@ -6491,7 +6489,7 @@
         <v>0.047559753060340881</v>
       </c>
       <c r="C584" s="1">
-        <v>0.34712192416191101</v>
+        <v>0.34043601155281067</v>
       </c>
     </row>
     <row r="585">
@@ -6502,7 +6500,7 @@
         <v>0.036648828536272049</v>
       </c>
       <c r="C585" s="1">
-        <v>-0.28267383575439453</v>
+        <v>0.0089482609182596207</v>
       </c>
     </row>
     <row r="586">
@@ -6513,7 +6511,7 @@
         <v>0.10484205186367035</v>
       </c>
       <c r="C586" s="1">
-        <v>-0.14330944418907166</v>
+        <v>-0.064832098782062531</v>
       </c>
     </row>
     <row r="587">
@@ -6524,7 +6522,7 @@
         <v>-0.016087260097265244</v>
       </c>
       <c r="C587" s="1">
-        <v>-0.51358497142791748</v>
+        <v>-0.60450297594070435</v>
       </c>
     </row>
     <row r="588">
@@ -6535,7 +6533,7 @@
         <v>-0.015632636845111847</v>
       </c>
       <c r="C588" s="1">
-        <v>-0.030288597568869591</v>
+        <v>-0.060199208557605744</v>
       </c>
     </row>
     <row r="589">
@@ -6546,7 +6544,7 @@
         <v>-0.059730920940637589</v>
       </c>
       <c r="C589" s="1">
-        <v>0.23167720437049866</v>
+        <v>0.29220545291900635</v>
       </c>
     </row>
   </sheetData>
